--- a/exel need/SMMEMBER .xlsx
+++ b/exel need/SMMEMBER .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\YLY\web2\exel need\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967CEFD0-B57A-4197-83A3-11D33B5C952C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79543234-0DCB-483D-92EB-AEB994ADABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1153,7 +1153,7 @@
       <c r="AH6" s="17"/>
       <c r="AI6" s="17"/>
       <c r="AJ6" s="9">
-        <f t="shared" ref="AJ6:AJ259" si="6">IFERROR(SUM(U6,V6,W6,X6,Y6,Z6,AA6,AB6,AC6,AD6,AE6,AF6,AG6,AH6,AI6)/T6*10,0)</f>
+        <f t="shared" ref="AJ6:AJ69" si="6">IFERROR(ROUND(SUM(AI6,AH6,AG6,AF6,AE6,AD6,AC6,AB6,AA6,Z6,Y6,X6,W6,V6,U6,)/T6*10,0),0)</f>
         <v>0</v>
       </c>
       <c r="AK6" s="7"/>
@@ -5569,7 +5569,7 @@
       <c r="AH70" s="17"/>
       <c r="AI70" s="17"/>
       <c r="AJ70" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AJ70:AJ133" si="11">IFERROR(ROUND(SUM(AI70,AH70,AG70,AF70,AE70,AD70,AC70,AB70,AA70,Z70,Y70,X70,W70,V70,U70,)/T70*10,0),0)</f>
         <v>0</v>
       </c>
       <c r="AK70" s="7"/>
@@ -5584,7 +5584,7 @@
         <v>0</v>
       </c>
       <c r="AP70" s="13" t="str">
-        <f t="shared" ref="AP70:AP133" si="11">IF(AN70&gt;=90,"A",IF(AN70&gt;=80,"B",IF(AN70&gt;=70,"C",IF(AN70&gt;=60,"D",IF(AN70&gt;0,"F"," ")))))</f>
+        <f t="shared" ref="AP70:AP133" si="12">IF(AN70&gt;=90,"A",IF(AN70&gt;=80,"B",IF(AN70&gt;=70,"C",IF(AN70&gt;=60,"D",IF(AN70&gt;0,"F"," ")))))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS70" s="14" t="str">
@@ -5638,7 +5638,7 @@
       <c r="AH71" s="17"/>
       <c r="AI71" s="17"/>
       <c r="AJ71" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK71" s="7"/>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="AP71" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS71" s="14" t="str">
@@ -5707,7 +5707,7 @@
       <c r="AH72" s="17"/>
       <c r="AI72" s="17"/>
       <c r="AJ72" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK72" s="7"/>
@@ -5722,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="AP72" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS72" s="14" t="str">
@@ -5776,7 +5776,7 @@
       <c r="AH73" s="17"/>
       <c r="AI73" s="17"/>
       <c r="AJ73" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK73" s="7"/>
@@ -5791,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="AP73" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS73" s="14" t="str">
@@ -5845,7 +5845,7 @@
       <c r="AH74" s="17"/>
       <c r="AI74" s="17"/>
       <c r="AJ74" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK74" s="7"/>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="AP74" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS74" s="14" t="str">
@@ -5914,7 +5914,7 @@
       <c r="AH75" s="17"/>
       <c r="AI75" s="17"/>
       <c r="AJ75" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK75" s="7"/>
@@ -5929,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="AP75" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS75" s="14" t="str">
@@ -5983,7 +5983,7 @@
       <c r="AH76" s="17"/>
       <c r="AI76" s="17"/>
       <c r="AJ76" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK76" s="7"/>
@@ -5998,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="AP76" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS76" s="14" t="str">
@@ -6052,7 +6052,7 @@
       <c r="AH77" s="17"/>
       <c r="AI77" s="17"/>
       <c r="AJ77" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK77" s="7"/>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="AP77" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS77" s="14" t="str">
@@ -6121,7 +6121,7 @@
       <c r="AH78" s="17"/>
       <c r="AI78" s="17"/>
       <c r="AJ78" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK78" s="7"/>
@@ -6136,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="AP78" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS78" s="14" t="str">
@@ -6190,7 +6190,7 @@
       <c r="AH79" s="17"/>
       <c r="AI79" s="17"/>
       <c r="AJ79" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK79" s="7"/>
@@ -6205,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="AP79" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS79" s="14" t="str">
@@ -6259,7 +6259,7 @@
       <c r="AH80" s="17"/>
       <c r="AI80" s="17"/>
       <c r="AJ80" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK80" s="7"/>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="AP80" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS80" s="14" t="str">
@@ -6328,7 +6328,7 @@
       <c r="AH81" s="17"/>
       <c r="AI81" s="17"/>
       <c r="AJ81" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK81" s="7"/>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="AP81" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS81" s="14" t="str">
@@ -6397,7 +6397,7 @@
       <c r="AH82" s="17"/>
       <c r="AI82" s="17"/>
       <c r="AJ82" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK82" s="7"/>
@@ -6412,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="AP82" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS82" s="14" t="str">
@@ -6466,7 +6466,7 @@
       <c r="AH83" s="17"/>
       <c r="AI83" s="17"/>
       <c r="AJ83" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK83" s="7"/>
@@ -6481,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="AP83" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS83" s="14" t="str">
@@ -6535,7 +6535,7 @@
       <c r="AH84" s="17"/>
       <c r="AI84" s="17"/>
       <c r="AJ84" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK84" s="7"/>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="AP84" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS84" s="14" t="str">
@@ -6604,7 +6604,7 @@
       <c r="AH85" s="17"/>
       <c r="AI85" s="17"/>
       <c r="AJ85" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK85" s="7"/>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AP85" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS85" s="14" t="str">
@@ -6673,7 +6673,7 @@
       <c r="AH86" s="17"/>
       <c r="AI86" s="17"/>
       <c r="AJ86" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK86" s="7"/>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="AP86" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS86" s="14" t="str">
@@ -6742,7 +6742,7 @@
       <c r="AH87" s="17"/>
       <c r="AI87" s="17"/>
       <c r="AJ87" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK87" s="7"/>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AP87" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS87" s="14" t="str">
@@ -6811,7 +6811,7 @@
       <c r="AH88" s="17"/>
       <c r="AI88" s="17"/>
       <c r="AJ88" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK88" s="7"/>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="AP88" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS88" s="14" t="str">
@@ -6880,7 +6880,7 @@
       <c r="AH89" s="17"/>
       <c r="AI89" s="17"/>
       <c r="AJ89" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK89" s="7"/>
@@ -6895,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="AP89" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS89" s="14" t="str">
@@ -6949,7 +6949,7 @@
       <c r="AH90" s="17"/>
       <c r="AI90" s="17"/>
       <c r="AJ90" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK90" s="7"/>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="AP90" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS90" s="14" t="str">
@@ -7018,7 +7018,7 @@
       <c r="AH91" s="17"/>
       <c r="AI91" s="17"/>
       <c r="AJ91" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK91" s="7"/>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="AP91" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS91" s="14" t="str">
@@ -7087,7 +7087,7 @@
       <c r="AH92" s="17"/>
       <c r="AI92" s="17"/>
       <c r="AJ92" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK92" s="7"/>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="AP92" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS92" s="14" t="str">
@@ -7156,7 +7156,7 @@
       <c r="AH93" s="17"/>
       <c r="AI93" s="17"/>
       <c r="AJ93" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK93" s="7"/>
@@ -7171,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="AP93" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS93" s="14" t="str">
@@ -7225,7 +7225,7 @@
       <c r="AH94" s="17"/>
       <c r="AI94" s="17"/>
       <c r="AJ94" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK94" s="7"/>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="AP94" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS94" s="14" t="str">
@@ -7294,7 +7294,7 @@
       <c r="AH95" s="17"/>
       <c r="AI95" s="17"/>
       <c r="AJ95" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK95" s="7"/>
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="AP95" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS95" s="14" t="str">
@@ -7363,7 +7363,7 @@
       <c r="AH96" s="17"/>
       <c r="AI96" s="17"/>
       <c r="AJ96" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK96" s="7"/>
@@ -7378,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="AP96" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS96" s="14" t="str">
@@ -7432,7 +7432,7 @@
       <c r="AH97" s="17"/>
       <c r="AI97" s="17"/>
       <c r="AJ97" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK97" s="7"/>
@@ -7447,7 +7447,7 @@
         <v>0</v>
       </c>
       <c r="AP97" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS97" s="14" t="str">
@@ -7501,7 +7501,7 @@
       <c r="AH98" s="17"/>
       <c r="AI98" s="17"/>
       <c r="AJ98" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK98" s="7"/>
@@ -7516,7 +7516,7 @@
         <v>0</v>
       </c>
       <c r="AP98" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS98" s="14" t="str">
@@ -7570,7 +7570,7 @@
       <c r="AH99" s="17"/>
       <c r="AI99" s="17"/>
       <c r="AJ99" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK99" s="7"/>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AP99" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS99" s="14" t="str">
@@ -7639,7 +7639,7 @@
       <c r="AH100" s="17"/>
       <c r="AI100" s="17"/>
       <c r="AJ100" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK100" s="7"/>
@@ -7654,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="AP100" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS100" s="14" t="str">
@@ -7708,7 +7708,7 @@
       <c r="AH101" s="17"/>
       <c r="AI101" s="17"/>
       <c r="AJ101" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK101" s="7"/>
@@ -7723,7 +7723,7 @@
         <v>0</v>
       </c>
       <c r="AP101" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS101" s="14" t="str">
@@ -7777,7 +7777,7 @@
       <c r="AH102" s="17"/>
       <c r="AI102" s="17"/>
       <c r="AJ102" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK102" s="7"/>
@@ -7792,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="AP102" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS102" s="14" t="str">
@@ -7846,7 +7846,7 @@
       <c r="AH103" s="17"/>
       <c r="AI103" s="17"/>
       <c r="AJ103" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK103" s="7"/>
@@ -7861,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="AP103" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS103" s="14" t="str">
@@ -7915,7 +7915,7 @@
       <c r="AH104" s="17"/>
       <c r="AI104" s="17"/>
       <c r="AJ104" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK104" s="7"/>
@@ -7930,7 +7930,7 @@
         <v>0</v>
       </c>
       <c r="AP104" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS104" s="14" t="str">
@@ -7984,7 +7984,7 @@
       <c r="AH105" s="17"/>
       <c r="AI105" s="17"/>
       <c r="AJ105" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK105" s="7"/>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="AP105" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS105" s="14" t="str">
@@ -8053,7 +8053,7 @@
       <c r="AH106" s="17"/>
       <c r="AI106" s="17"/>
       <c r="AJ106" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK106" s="7"/>
@@ -8068,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="AP106" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS106" s="14" t="str">
@@ -8122,7 +8122,7 @@
       <c r="AH107" s="17"/>
       <c r="AI107" s="17"/>
       <c r="AJ107" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK107" s="7"/>
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="AP107" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS107" s="14" t="str">
@@ -8191,7 +8191,7 @@
       <c r="AH108" s="17"/>
       <c r="AI108" s="17"/>
       <c r="AJ108" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK108" s="7"/>
@@ -8206,7 +8206,7 @@
         <v>0</v>
       </c>
       <c r="AP108" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS108" s="14" t="str">
@@ -8260,7 +8260,7 @@
       <c r="AH109" s="17"/>
       <c r="AI109" s="17"/>
       <c r="AJ109" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK109" s="7"/>
@@ -8275,7 +8275,7 @@
         <v>0</v>
       </c>
       <c r="AP109" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS109" s="14" t="str">
@@ -8329,7 +8329,7 @@
       <c r="AH110" s="17"/>
       <c r="AI110" s="17"/>
       <c r="AJ110" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK110" s="7"/>
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="AP110" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS110" s="14" t="str">
@@ -8398,7 +8398,7 @@
       <c r="AH111" s="17"/>
       <c r="AI111" s="17"/>
       <c r="AJ111" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK111" s="7"/>
@@ -8413,7 +8413,7 @@
         <v>0</v>
       </c>
       <c r="AP111" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS111" s="14" t="str">
@@ -8467,7 +8467,7 @@
       <c r="AH112" s="17"/>
       <c r="AI112" s="17"/>
       <c r="AJ112" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK112" s="7"/>
@@ -8482,7 +8482,7 @@
         <v>0</v>
       </c>
       <c r="AP112" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS112" s="14" t="str">
@@ -8536,7 +8536,7 @@
       <c r="AH113" s="17"/>
       <c r="AI113" s="17"/>
       <c r="AJ113" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK113" s="7"/>
@@ -8551,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="AP113" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS113" s="14" t="str">
@@ -8605,7 +8605,7 @@
       <c r="AH114" s="17"/>
       <c r="AI114" s="17"/>
       <c r="AJ114" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK114" s="7"/>
@@ -8620,7 +8620,7 @@
         <v>0</v>
       </c>
       <c r="AP114" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS114" s="14" t="str">
@@ -8674,7 +8674,7 @@
       <c r="AH115" s="17"/>
       <c r="AI115" s="17"/>
       <c r="AJ115" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK115" s="7"/>
@@ -8689,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="AP115" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS115" s="14" t="str">
@@ -8743,7 +8743,7 @@
       <c r="AH116" s="17"/>
       <c r="AI116" s="17"/>
       <c r="AJ116" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK116" s="7"/>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="AP116" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS116" s="14" t="str">
@@ -8812,7 +8812,7 @@
       <c r="AH117" s="17"/>
       <c r="AI117" s="17"/>
       <c r="AJ117" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK117" s="7"/>
@@ -8827,7 +8827,7 @@
         <v>0</v>
       </c>
       <c r="AP117" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS117" s="14" t="str">
@@ -8881,7 +8881,7 @@
       <c r="AH118" s="17"/>
       <c r="AI118" s="17"/>
       <c r="AJ118" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK118" s="7"/>
@@ -8896,7 +8896,7 @@
         <v>0</v>
       </c>
       <c r="AP118" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS118" s="14" t="str">
@@ -8950,7 +8950,7 @@
       <c r="AH119" s="17"/>
       <c r="AI119" s="17"/>
       <c r="AJ119" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK119" s="7"/>
@@ -8965,7 +8965,7 @@
         <v>0</v>
       </c>
       <c r="AP119" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS119" s="14" t="str">
@@ -9019,7 +9019,7 @@
       <c r="AH120" s="17"/>
       <c r="AI120" s="17"/>
       <c r="AJ120" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK120" s="7"/>
@@ -9034,7 +9034,7 @@
         <v>0</v>
       </c>
       <c r="AP120" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS120" s="14" t="str">
@@ -9088,7 +9088,7 @@
       <c r="AH121" s="17"/>
       <c r="AI121" s="17"/>
       <c r="AJ121" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK121" s="7"/>
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="AP121" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS121" s="14" t="str">
@@ -9157,7 +9157,7 @@
       <c r="AH122" s="17"/>
       <c r="AI122" s="17"/>
       <c r="AJ122" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK122" s="7"/>
@@ -9172,7 +9172,7 @@
         <v>0</v>
       </c>
       <c r="AP122" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS122" s="14" t="str">
@@ -9226,7 +9226,7 @@
       <c r="AH123" s="17"/>
       <c r="AI123" s="17"/>
       <c r="AJ123" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK123" s="7"/>
@@ -9241,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="AP123" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS123" s="14" t="str">
@@ -9295,7 +9295,7 @@
       <c r="AH124" s="17"/>
       <c r="AI124" s="17"/>
       <c r="AJ124" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK124" s="7"/>
@@ -9310,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="AP124" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS124" s="14" t="str">
@@ -9364,7 +9364,7 @@
       <c r="AH125" s="17"/>
       <c r="AI125" s="17"/>
       <c r="AJ125" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK125" s="7"/>
@@ -9379,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="AP125" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS125" s="14" t="str">
@@ -9433,7 +9433,7 @@
       <c r="AH126" s="17"/>
       <c r="AI126" s="17"/>
       <c r="AJ126" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK126" s="7"/>
@@ -9448,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="AP126" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS126" s="14" t="str">
@@ -9502,7 +9502,7 @@
       <c r="AH127" s="17"/>
       <c r="AI127" s="17"/>
       <c r="AJ127" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK127" s="7"/>
@@ -9517,7 +9517,7 @@
         <v>0</v>
       </c>
       <c r="AP127" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS127" s="14" t="str">
@@ -9571,7 +9571,7 @@
       <c r="AH128" s="17"/>
       <c r="AI128" s="17"/>
       <c r="AJ128" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK128" s="7"/>
@@ -9586,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="AP128" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS128" s="14" t="str">
@@ -9640,7 +9640,7 @@
       <c r="AH129" s="17"/>
       <c r="AI129" s="17"/>
       <c r="AJ129" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK129" s="7"/>
@@ -9655,7 +9655,7 @@
         <v>0</v>
       </c>
       <c r="AP129" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS129" s="14" t="str">
@@ -9709,7 +9709,7 @@
       <c r="AH130" s="17"/>
       <c r="AI130" s="17"/>
       <c r="AJ130" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK130" s="7"/>
@@ -9724,7 +9724,7 @@
         <v>0</v>
       </c>
       <c r="AP130" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS130" s="14" t="str">
@@ -9778,7 +9778,7 @@
       <c r="AH131" s="17"/>
       <c r="AI131" s="17"/>
       <c r="AJ131" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK131" s="7"/>
@@ -9793,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="AP131" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS131" s="14" t="str">
@@ -9847,7 +9847,7 @@
       <c r="AH132" s="17"/>
       <c r="AI132" s="17"/>
       <c r="AJ132" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK132" s="7"/>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="AP132" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS132" s="14" t="str">
@@ -9916,7 +9916,7 @@
       <c r="AH133" s="17"/>
       <c r="AI133" s="17"/>
       <c r="AJ133" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK133" s="7"/>
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="AP133" s="13" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS133" s="14" t="str">
@@ -9943,7 +9943,7 @@
       <c r="A134" s="15"/>
       <c r="B134" s="7"/>
       <c r="C134" s="8" t="str">
-        <f t="shared" ref="C134:C197" si="12">IF(COUNTA($D$3:$R$3)=0, "", COUNTA($D$3:$R$3))</f>
+        <f t="shared" ref="C134:C197" si="13">IF(COUNTA($D$3:$R$3)=0, "", COUNTA($D$3:$R$3))</f>
         <v/>
       </c>
       <c r="D134" s="17"/>
@@ -9962,11 +9962,11 @@
       <c r="Q134" s="17"/>
       <c r="R134" s="17"/>
       <c r="S134" s="9">
-        <f t="shared" ref="S134:S197" si="13">IFERROR(ROUND(SUM(D134,E134,F134,G134,H134,I134,J134,K134,L134,M134,N134,O134,P134,Q134,R134)/C134*20,0),0)</f>
+        <f t="shared" ref="S134:S197" si="14">IFERROR(ROUND(SUM(D134,E134,F134,G134,H134,I134,J134,K134,L134,M134,N134,O134,P134,Q134,R134)/C134*20,0),0)</f>
         <v>0</v>
       </c>
       <c r="T134" s="8" t="str">
-        <f t="shared" ref="T134:T197" si="14">IF(COUNTA($U$3:$AI$3 )=0, "", COUNTA($U$3:$AI$3))</f>
+        <f t="shared" ref="T134:T197" si="15">IF(COUNTA($U$3:$AI$3 )=0, "", COUNTA($U$3:$AI$3))</f>
         <v/>
       </c>
       <c r="U134" s="17"/>
@@ -9985,7 +9985,7 @@
       <c r="AH134" s="17"/>
       <c r="AI134" s="17"/>
       <c r="AJ134" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AJ134:AJ197" si="16">IFERROR(ROUND(SUM(AI134,AH134,AG134,AF134,AE134,AD134,AC134,AB134,AA134,Z134,Y134,X134,W134,V134,U134,)/T134*10,0),0)</f>
         <v>0</v>
       </c>
       <c r="AK134" s="7"/>
@@ -10000,7 +10000,7 @@
         <v>0</v>
       </c>
       <c r="AP134" s="13" t="str">
-        <f t="shared" ref="AP134:AP197" si="15">IF(AN134&gt;=90,"A",IF(AN134&gt;=80,"B",IF(AN134&gt;=70,"C",IF(AN134&gt;=60,"D",IF(AN134&gt;0,"F"," ")))))</f>
+        <f t="shared" ref="AP134:AP197" si="17">IF(AN134&gt;=90,"A",IF(AN134&gt;=80,"B",IF(AN134&gt;=70,"C",IF(AN134&gt;=60,"D",IF(AN134&gt;0,"F"," ")))))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS134" s="14" t="str">
@@ -10012,7 +10012,7 @@
       <c r="A135" s="6"/>
       <c r="B135" s="7"/>
       <c r="C135" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D135" s="17"/>
@@ -10031,11 +10031,11 @@
       <c r="Q135" s="17"/>
       <c r="R135" s="17"/>
       <c r="S135" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T135" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U135" s="17"/>
@@ -10054,7 +10054,7 @@
       <c r="AH135" s="17"/>
       <c r="AI135" s="17"/>
       <c r="AJ135" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK135" s="7"/>
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="AP135" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS135" s="14" t="str">
@@ -10081,7 +10081,7 @@
       <c r="A136" s="15"/>
       <c r="B136" s="7"/>
       <c r="C136" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D136" s="17"/>
@@ -10100,11 +10100,11 @@
       <c r="Q136" s="17"/>
       <c r="R136" s="17"/>
       <c r="S136" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T136" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U136" s="17"/>
@@ -10123,7 +10123,7 @@
       <c r="AH136" s="17"/>
       <c r="AI136" s="17"/>
       <c r="AJ136" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK136" s="7"/>
@@ -10138,7 +10138,7 @@
         <v>0</v>
       </c>
       <c r="AP136" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS136" s="14" t="str">
@@ -10150,7 +10150,7 @@
       <c r="A137" s="6"/>
       <c r="B137" s="7"/>
       <c r="C137" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D137" s="17"/>
@@ -10169,11 +10169,11 @@
       <c r="Q137" s="17"/>
       <c r="R137" s="17"/>
       <c r="S137" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T137" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U137" s="17"/>
@@ -10192,7 +10192,7 @@
       <c r="AH137" s="17"/>
       <c r="AI137" s="17"/>
       <c r="AJ137" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK137" s="7"/>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="AP137" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS137" s="14" t="str">
@@ -10219,7 +10219,7 @@
       <c r="A138" s="15"/>
       <c r="B138" s="7"/>
       <c r="C138" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D138" s="17"/>
@@ -10238,11 +10238,11 @@
       <c r="Q138" s="17"/>
       <c r="R138" s="17"/>
       <c r="S138" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T138" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U138" s="17"/>
@@ -10261,7 +10261,7 @@
       <c r="AH138" s="17"/>
       <c r="AI138" s="17"/>
       <c r="AJ138" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK138" s="7"/>
@@ -10276,7 +10276,7 @@
         <v>0</v>
       </c>
       <c r="AP138" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS138" s="14" t="str">
@@ -10288,7 +10288,7 @@
       <c r="A139" s="6"/>
       <c r="B139" s="7"/>
       <c r="C139" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D139" s="17"/>
@@ -10307,11 +10307,11 @@
       <c r="Q139" s="17"/>
       <c r="R139" s="17"/>
       <c r="S139" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T139" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U139" s="17"/>
@@ -10330,7 +10330,7 @@
       <c r="AH139" s="17"/>
       <c r="AI139" s="17"/>
       <c r="AJ139" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK139" s="7"/>
@@ -10345,7 +10345,7 @@
         <v>0</v>
       </c>
       <c r="AP139" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS139" s="14" t="str">
@@ -10357,7 +10357,7 @@
       <c r="A140" s="15"/>
       <c r="B140" s="7"/>
       <c r="C140" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D140" s="17"/>
@@ -10376,11 +10376,11 @@
       <c r="Q140" s="17"/>
       <c r="R140" s="17"/>
       <c r="S140" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T140" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U140" s="17"/>
@@ -10399,7 +10399,7 @@
       <c r="AH140" s="17"/>
       <c r="AI140" s="17"/>
       <c r="AJ140" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK140" s="7"/>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="AP140" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS140" s="14" t="str">
@@ -10426,7 +10426,7 @@
       <c r="A141" s="6"/>
       <c r="B141" s="7"/>
       <c r="C141" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D141" s="17"/>
@@ -10445,11 +10445,11 @@
       <c r="Q141" s="17"/>
       <c r="R141" s="17"/>
       <c r="S141" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T141" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U141" s="17"/>
@@ -10468,7 +10468,7 @@
       <c r="AH141" s="17"/>
       <c r="AI141" s="17"/>
       <c r="AJ141" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK141" s="7"/>
@@ -10483,7 +10483,7 @@
         <v>0</v>
       </c>
       <c r="AP141" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS141" s="14" t="str">
@@ -10495,7 +10495,7 @@
       <c r="A142" s="15"/>
       <c r="B142" s="7"/>
       <c r="C142" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D142" s="17"/>
@@ -10514,11 +10514,11 @@
       <c r="Q142" s="17"/>
       <c r="R142" s="17"/>
       <c r="S142" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T142" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U142" s="17"/>
@@ -10537,7 +10537,7 @@
       <c r="AH142" s="17"/>
       <c r="AI142" s="17"/>
       <c r="AJ142" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK142" s="7"/>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AP142" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS142" s="14" t="str">
@@ -10564,7 +10564,7 @@
       <c r="A143" s="6"/>
       <c r="B143" s="7"/>
       <c r="C143" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D143" s="17"/>
@@ -10583,11 +10583,11 @@
       <c r="Q143" s="17"/>
       <c r="R143" s="17"/>
       <c r="S143" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T143" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U143" s="17"/>
@@ -10606,7 +10606,7 @@
       <c r="AH143" s="17"/>
       <c r="AI143" s="17"/>
       <c r="AJ143" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK143" s="7"/>
@@ -10621,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="AP143" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS143" s="14" t="str">
@@ -10633,7 +10633,7 @@
       <c r="A144" s="15"/>
       <c r="B144" s="7"/>
       <c r="C144" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D144" s="17"/>
@@ -10652,11 +10652,11 @@
       <c r="Q144" s="17"/>
       <c r="R144" s="17"/>
       <c r="S144" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T144" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U144" s="17"/>
@@ -10675,7 +10675,7 @@
       <c r="AH144" s="17"/>
       <c r="AI144" s="17"/>
       <c r="AJ144" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK144" s="7"/>
@@ -10690,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="AP144" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS144" s="14" t="str">
@@ -10702,7 +10702,7 @@
       <c r="A145" s="6"/>
       <c r="B145" s="7"/>
       <c r="C145" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D145" s="17"/>
@@ -10721,11 +10721,11 @@
       <c r="Q145" s="17"/>
       <c r="R145" s="17"/>
       <c r="S145" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T145" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U145" s="17"/>
@@ -10744,7 +10744,7 @@
       <c r="AH145" s="17"/>
       <c r="AI145" s="17"/>
       <c r="AJ145" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK145" s="7"/>
@@ -10759,7 +10759,7 @@
         <v>0</v>
       </c>
       <c r="AP145" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS145" s="14" t="str">
@@ -10771,7 +10771,7 @@
       <c r="A146" s="15"/>
       <c r="B146" s="7"/>
       <c r="C146" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D146" s="17"/>
@@ -10790,11 +10790,11 @@
       <c r="Q146" s="17"/>
       <c r="R146" s="17"/>
       <c r="S146" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T146" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U146" s="17"/>
@@ -10813,7 +10813,7 @@
       <c r="AH146" s="17"/>
       <c r="AI146" s="17"/>
       <c r="AJ146" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK146" s="7"/>
@@ -10828,7 +10828,7 @@
         <v>0</v>
       </c>
       <c r="AP146" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS146" s="14" t="str">
@@ -10840,7 +10840,7 @@
       <c r="A147" s="6"/>
       <c r="B147" s="7"/>
       <c r="C147" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D147" s="17"/>
@@ -10859,11 +10859,11 @@
       <c r="Q147" s="17"/>
       <c r="R147" s="17"/>
       <c r="S147" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T147" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U147" s="17"/>
@@ -10882,7 +10882,7 @@
       <c r="AH147" s="17"/>
       <c r="AI147" s="17"/>
       <c r="AJ147" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK147" s="7"/>
@@ -10897,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="AP147" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS147" s="14" t="str">
@@ -10909,7 +10909,7 @@
       <c r="A148" s="15"/>
       <c r="B148" s="7"/>
       <c r="C148" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D148" s="17"/>
@@ -10928,11 +10928,11 @@
       <c r="Q148" s="17"/>
       <c r="R148" s="17"/>
       <c r="S148" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T148" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U148" s="17"/>
@@ -10951,7 +10951,7 @@
       <c r="AH148" s="17"/>
       <c r="AI148" s="17"/>
       <c r="AJ148" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK148" s="7"/>
@@ -10966,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="AP148" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS148" s="14" t="str">
@@ -10978,7 +10978,7 @@
       <c r="A149" s="6"/>
       <c r="B149" s="7"/>
       <c r="C149" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D149" s="17"/>
@@ -10997,11 +10997,11 @@
       <c r="Q149" s="17"/>
       <c r="R149" s="17"/>
       <c r="S149" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T149" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U149" s="17"/>
@@ -11020,7 +11020,7 @@
       <c r="AH149" s="17"/>
       <c r="AI149" s="17"/>
       <c r="AJ149" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK149" s="7"/>
@@ -11035,7 +11035,7 @@
         <v>0</v>
       </c>
       <c r="AP149" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS149" s="14" t="str">
@@ -11047,7 +11047,7 @@
       <c r="A150" s="15"/>
       <c r="B150" s="7"/>
       <c r="C150" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D150" s="17"/>
@@ -11066,11 +11066,11 @@
       <c r="Q150" s="17"/>
       <c r="R150" s="17"/>
       <c r="S150" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T150" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U150" s="17"/>
@@ -11089,7 +11089,7 @@
       <c r="AH150" s="17"/>
       <c r="AI150" s="17"/>
       <c r="AJ150" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK150" s="7"/>
@@ -11104,7 +11104,7 @@
         <v>0</v>
       </c>
       <c r="AP150" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS150" s="14" t="str">
@@ -11116,7 +11116,7 @@
       <c r="A151" s="6"/>
       <c r="B151" s="7"/>
       <c r="C151" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D151" s="17"/>
@@ -11135,11 +11135,11 @@
       <c r="Q151" s="17"/>
       <c r="R151" s="17"/>
       <c r="S151" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T151" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U151" s="17"/>
@@ -11158,7 +11158,7 @@
       <c r="AH151" s="17"/>
       <c r="AI151" s="17"/>
       <c r="AJ151" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK151" s="7"/>
@@ -11173,7 +11173,7 @@
         <v>0</v>
       </c>
       <c r="AP151" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS151" s="14" t="str">
@@ -11185,7 +11185,7 @@
       <c r="A152" s="15"/>
       <c r="B152" s="7"/>
       <c r="C152" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D152" s="17"/>
@@ -11204,11 +11204,11 @@
       <c r="Q152" s="17"/>
       <c r="R152" s="17"/>
       <c r="S152" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T152" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U152" s="17"/>
@@ -11227,7 +11227,7 @@
       <c r="AH152" s="17"/>
       <c r="AI152" s="17"/>
       <c r="AJ152" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK152" s="7"/>
@@ -11242,7 +11242,7 @@
         <v>0</v>
       </c>
       <c r="AP152" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS152" s="14" t="str">
@@ -11254,7 +11254,7 @@
       <c r="A153" s="6"/>
       <c r="B153" s="7"/>
       <c r="C153" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D153" s="17"/>
@@ -11273,11 +11273,11 @@
       <c r="Q153" s="17"/>
       <c r="R153" s="17"/>
       <c r="S153" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T153" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U153" s="17"/>
@@ -11296,7 +11296,7 @@
       <c r="AH153" s="17"/>
       <c r="AI153" s="17"/>
       <c r="AJ153" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK153" s="7"/>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="AP153" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS153" s="14" t="str">
@@ -11323,7 +11323,7 @@
       <c r="A154" s="15"/>
       <c r="B154" s="7"/>
       <c r="C154" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D154" s="17"/>
@@ -11342,11 +11342,11 @@
       <c r="Q154" s="17"/>
       <c r="R154" s="17"/>
       <c r="S154" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T154" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U154" s="17"/>
@@ -11365,7 +11365,7 @@
       <c r="AH154" s="17"/>
       <c r="AI154" s="17"/>
       <c r="AJ154" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK154" s="7"/>
@@ -11380,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="AP154" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS154" s="14" t="str">
@@ -11392,7 +11392,7 @@
       <c r="A155" s="6"/>
       <c r="B155" s="7"/>
       <c r="C155" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D155" s="17"/>
@@ -11411,11 +11411,11 @@
       <c r="Q155" s="17"/>
       <c r="R155" s="17"/>
       <c r="S155" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T155" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U155" s="17"/>
@@ -11434,7 +11434,7 @@
       <c r="AH155" s="17"/>
       <c r="AI155" s="17"/>
       <c r="AJ155" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK155" s="7"/>
@@ -11449,7 +11449,7 @@
         <v>0</v>
       </c>
       <c r="AP155" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS155" s="14" t="str">
@@ -11461,7 +11461,7 @@
       <c r="A156" s="15"/>
       <c r="B156" s="7"/>
       <c r="C156" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D156" s="17"/>
@@ -11480,11 +11480,11 @@
       <c r="Q156" s="17"/>
       <c r="R156" s="17"/>
       <c r="S156" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T156" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U156" s="17"/>
@@ -11503,7 +11503,7 @@
       <c r="AH156" s="17"/>
       <c r="AI156" s="17"/>
       <c r="AJ156" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK156" s="7"/>
@@ -11518,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="AP156" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS156" s="14" t="str">
@@ -11530,7 +11530,7 @@
       <c r="A157" s="6"/>
       <c r="B157" s="7"/>
       <c r="C157" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D157" s="17"/>
@@ -11549,11 +11549,11 @@
       <c r="Q157" s="17"/>
       <c r="R157" s="17"/>
       <c r="S157" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T157" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U157" s="17"/>
@@ -11572,7 +11572,7 @@
       <c r="AH157" s="17"/>
       <c r="AI157" s="17"/>
       <c r="AJ157" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK157" s="7"/>
@@ -11587,7 +11587,7 @@
         <v>0</v>
       </c>
       <c r="AP157" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS157" s="14" t="str">
@@ -11599,7 +11599,7 @@
       <c r="A158" s="15"/>
       <c r="B158" s="7"/>
       <c r="C158" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D158" s="17"/>
@@ -11618,11 +11618,11 @@
       <c r="Q158" s="17"/>
       <c r="R158" s="17"/>
       <c r="S158" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T158" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U158" s="17"/>
@@ -11641,7 +11641,7 @@
       <c r="AH158" s="17"/>
       <c r="AI158" s="17"/>
       <c r="AJ158" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK158" s="7"/>
@@ -11656,7 +11656,7 @@
         <v>0</v>
       </c>
       <c r="AP158" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS158" s="14" t="str">
@@ -11668,7 +11668,7 @@
       <c r="A159" s="6"/>
       <c r="B159" s="7"/>
       <c r="C159" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D159" s="17"/>
@@ -11687,11 +11687,11 @@
       <c r="Q159" s="17"/>
       <c r="R159" s="17"/>
       <c r="S159" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T159" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U159" s="17"/>
@@ -11710,7 +11710,7 @@
       <c r="AH159" s="17"/>
       <c r="AI159" s="17"/>
       <c r="AJ159" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK159" s="7"/>
@@ -11725,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="AP159" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS159" s="14" t="str">
@@ -11737,7 +11737,7 @@
       <c r="A160" s="15"/>
       <c r="B160" s="7"/>
       <c r="C160" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D160" s="17"/>
@@ -11756,11 +11756,11 @@
       <c r="Q160" s="17"/>
       <c r="R160" s="17"/>
       <c r="S160" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T160" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U160" s="17"/>
@@ -11779,7 +11779,7 @@
       <c r="AH160" s="17"/>
       <c r="AI160" s="17"/>
       <c r="AJ160" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK160" s="7"/>
@@ -11794,7 +11794,7 @@
         <v>0</v>
       </c>
       <c r="AP160" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS160" s="14" t="str">
@@ -11806,7 +11806,7 @@
       <c r="A161" s="6"/>
       <c r="B161" s="7"/>
       <c r="C161" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D161" s="17"/>
@@ -11825,11 +11825,11 @@
       <c r="Q161" s="17"/>
       <c r="R161" s="17"/>
       <c r="S161" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T161" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U161" s="17"/>
@@ -11848,7 +11848,7 @@
       <c r="AH161" s="17"/>
       <c r="AI161" s="17"/>
       <c r="AJ161" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK161" s="7"/>
@@ -11863,7 +11863,7 @@
         <v>0</v>
       </c>
       <c r="AP161" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS161" s="14" t="str">
@@ -11875,7 +11875,7 @@
       <c r="A162" s="15"/>
       <c r="B162" s="7"/>
       <c r="C162" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D162" s="17"/>
@@ -11894,11 +11894,11 @@
       <c r="Q162" s="17"/>
       <c r="R162" s="17"/>
       <c r="S162" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T162" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U162" s="17"/>
@@ -11917,7 +11917,7 @@
       <c r="AH162" s="17"/>
       <c r="AI162" s="17"/>
       <c r="AJ162" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK162" s="7"/>
@@ -11932,7 +11932,7 @@
         <v>0</v>
       </c>
       <c r="AP162" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS162" s="14" t="str">
@@ -11944,7 +11944,7 @@
       <c r="A163" s="6"/>
       <c r="B163" s="7"/>
       <c r="C163" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D163" s="17"/>
@@ -11963,11 +11963,11 @@
       <c r="Q163" s="17"/>
       <c r="R163" s="17"/>
       <c r="S163" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T163" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U163" s="17"/>
@@ -11986,7 +11986,7 @@
       <c r="AH163" s="17"/>
       <c r="AI163" s="17"/>
       <c r="AJ163" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK163" s="7"/>
@@ -12001,7 +12001,7 @@
         <v>0</v>
       </c>
       <c r="AP163" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS163" s="14" t="str">
@@ -12013,7 +12013,7 @@
       <c r="A164" s="15"/>
       <c r="B164" s="7"/>
       <c r="C164" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D164" s="17"/>
@@ -12032,11 +12032,11 @@
       <c r="Q164" s="17"/>
       <c r="R164" s="17"/>
       <c r="S164" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T164" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U164" s="17"/>
@@ -12055,7 +12055,7 @@
       <c r="AH164" s="17"/>
       <c r="AI164" s="17"/>
       <c r="AJ164" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK164" s="7"/>
@@ -12070,7 +12070,7 @@
         <v>0</v>
       </c>
       <c r="AP164" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS164" s="14" t="str">
@@ -12082,7 +12082,7 @@
       <c r="A165" s="6"/>
       <c r="B165" s="7"/>
       <c r="C165" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D165" s="17"/>
@@ -12101,11 +12101,11 @@
       <c r="Q165" s="17"/>
       <c r="R165" s="17"/>
       <c r="S165" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T165" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U165" s="17"/>
@@ -12124,7 +12124,7 @@
       <c r="AH165" s="17"/>
       <c r="AI165" s="17"/>
       <c r="AJ165" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK165" s="7"/>
@@ -12139,7 +12139,7 @@
         <v>0</v>
       </c>
       <c r="AP165" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS165" s="14" t="str">
@@ -12151,7 +12151,7 @@
       <c r="A166" s="15"/>
       <c r="B166" s="7"/>
       <c r="C166" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D166" s="17"/>
@@ -12170,11 +12170,11 @@
       <c r="Q166" s="17"/>
       <c r="R166" s="17"/>
       <c r="S166" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T166" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U166" s="17"/>
@@ -12193,7 +12193,7 @@
       <c r="AH166" s="17"/>
       <c r="AI166" s="17"/>
       <c r="AJ166" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK166" s="7"/>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="AP166" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS166" s="14" t="str">
@@ -12220,7 +12220,7 @@
       <c r="A167" s="6"/>
       <c r="B167" s="7"/>
       <c r="C167" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D167" s="17"/>
@@ -12239,11 +12239,11 @@
       <c r="Q167" s="17"/>
       <c r="R167" s="17"/>
       <c r="S167" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T167" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U167" s="17"/>
@@ -12262,7 +12262,7 @@
       <c r="AH167" s="17"/>
       <c r="AI167" s="17"/>
       <c r="AJ167" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK167" s="7"/>
@@ -12277,7 +12277,7 @@
         <v>0</v>
       </c>
       <c r="AP167" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS167" s="14" t="str">
@@ -12289,7 +12289,7 @@
       <c r="A168" s="15"/>
       <c r="B168" s="7"/>
       <c r="C168" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D168" s="17"/>
@@ -12308,11 +12308,11 @@
       <c r="Q168" s="17"/>
       <c r="R168" s="17"/>
       <c r="S168" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T168" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U168" s="17"/>
@@ -12331,7 +12331,7 @@
       <c r="AH168" s="17"/>
       <c r="AI168" s="17"/>
       <c r="AJ168" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK168" s="7"/>
@@ -12346,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="AP168" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS168" s="14" t="str">
@@ -12358,7 +12358,7 @@
       <c r="A169" s="6"/>
       <c r="B169" s="7"/>
       <c r="C169" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D169" s="17"/>
@@ -12377,11 +12377,11 @@
       <c r="Q169" s="17"/>
       <c r="R169" s="17"/>
       <c r="S169" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T169" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U169" s="17"/>
@@ -12400,7 +12400,7 @@
       <c r="AH169" s="17"/>
       <c r="AI169" s="17"/>
       <c r="AJ169" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK169" s="7"/>
@@ -12415,7 +12415,7 @@
         <v>0</v>
       </c>
       <c r="AP169" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS169" s="14" t="str">
@@ -12427,7 +12427,7 @@
       <c r="A170" s="15"/>
       <c r="B170" s="7"/>
       <c r="C170" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D170" s="17"/>
@@ -12446,11 +12446,11 @@
       <c r="Q170" s="17"/>
       <c r="R170" s="17"/>
       <c r="S170" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T170" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U170" s="17"/>
@@ -12469,7 +12469,7 @@
       <c r="AH170" s="17"/>
       <c r="AI170" s="17"/>
       <c r="AJ170" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK170" s="7"/>
@@ -12484,7 +12484,7 @@
         <v>0</v>
       </c>
       <c r="AP170" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS170" s="14" t="str">
@@ -12496,7 +12496,7 @@
       <c r="A171" s="6"/>
       <c r="B171" s="7"/>
       <c r="C171" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D171" s="17"/>
@@ -12515,11 +12515,11 @@
       <c r="Q171" s="17"/>
       <c r="R171" s="17"/>
       <c r="S171" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T171" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U171" s="17"/>
@@ -12538,7 +12538,7 @@
       <c r="AH171" s="17"/>
       <c r="AI171" s="17"/>
       <c r="AJ171" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK171" s="7"/>
@@ -12553,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="AP171" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS171" s="14" t="str">
@@ -12565,7 +12565,7 @@
       <c r="A172" s="15"/>
       <c r="B172" s="7"/>
       <c r="C172" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D172" s="17"/>
@@ -12584,11 +12584,11 @@
       <c r="Q172" s="17"/>
       <c r="R172" s="17"/>
       <c r="S172" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T172" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U172" s="17"/>
@@ -12607,7 +12607,7 @@
       <c r="AH172" s="17"/>
       <c r="AI172" s="17"/>
       <c r="AJ172" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK172" s="7"/>
@@ -12622,7 +12622,7 @@
         <v>0</v>
       </c>
       <c r="AP172" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS172" s="14" t="str">
@@ -12634,7 +12634,7 @@
       <c r="A173" s="6"/>
       <c r="B173" s="7"/>
       <c r="C173" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D173" s="17"/>
@@ -12653,11 +12653,11 @@
       <c r="Q173" s="17"/>
       <c r="R173" s="17"/>
       <c r="S173" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T173" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U173" s="17"/>
@@ -12676,7 +12676,7 @@
       <c r="AH173" s="17"/>
       <c r="AI173" s="17"/>
       <c r="AJ173" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK173" s="7"/>
@@ -12691,7 +12691,7 @@
         <v>0</v>
       </c>
       <c r="AP173" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS173" s="14" t="str">
@@ -12703,7 +12703,7 @@
       <c r="A174" s="15"/>
       <c r="B174" s="7"/>
       <c r="C174" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D174" s="17"/>
@@ -12722,11 +12722,11 @@
       <c r="Q174" s="17"/>
       <c r="R174" s="17"/>
       <c r="S174" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T174" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U174" s="17"/>
@@ -12745,7 +12745,7 @@
       <c r="AH174" s="17"/>
       <c r="AI174" s="17"/>
       <c r="AJ174" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK174" s="7"/>
@@ -12760,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="AP174" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS174" s="14" t="str">
@@ -12772,7 +12772,7 @@
       <c r="A175" s="6"/>
       <c r="B175" s="7"/>
       <c r="C175" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D175" s="17"/>
@@ -12791,11 +12791,11 @@
       <c r="Q175" s="17"/>
       <c r="R175" s="17"/>
       <c r="S175" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T175" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U175" s="17"/>
@@ -12814,7 +12814,7 @@
       <c r="AH175" s="17"/>
       <c r="AI175" s="17"/>
       <c r="AJ175" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK175" s="7"/>
@@ -12829,7 +12829,7 @@
         <v>0</v>
       </c>
       <c r="AP175" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS175" s="14" t="str">
@@ -12841,7 +12841,7 @@
       <c r="A176" s="15"/>
       <c r="B176" s="7"/>
       <c r="C176" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D176" s="17"/>
@@ -12860,11 +12860,11 @@
       <c r="Q176" s="17"/>
       <c r="R176" s="17"/>
       <c r="S176" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T176" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U176" s="17"/>
@@ -12883,7 +12883,7 @@
       <c r="AH176" s="17"/>
       <c r="AI176" s="17"/>
       <c r="AJ176" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK176" s="7"/>
@@ -12898,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="AP176" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS176" s="14" t="str">
@@ -12910,7 +12910,7 @@
       <c r="A177" s="6"/>
       <c r="B177" s="7"/>
       <c r="C177" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D177" s="17"/>
@@ -12929,11 +12929,11 @@
       <c r="Q177" s="17"/>
       <c r="R177" s="17"/>
       <c r="S177" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T177" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U177" s="17"/>
@@ -12952,7 +12952,7 @@
       <c r="AH177" s="17"/>
       <c r="AI177" s="17"/>
       <c r="AJ177" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK177" s="7"/>
@@ -12967,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="AP177" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS177" s="14" t="str">
@@ -12979,7 +12979,7 @@
       <c r="A178" s="15"/>
       <c r="B178" s="7"/>
       <c r="C178" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D178" s="17"/>
@@ -12998,11 +12998,11 @@
       <c r="Q178" s="17"/>
       <c r="R178" s="17"/>
       <c r="S178" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T178" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U178" s="17"/>
@@ -13021,7 +13021,7 @@
       <c r="AH178" s="17"/>
       <c r="AI178" s="17"/>
       <c r="AJ178" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK178" s="7"/>
@@ -13036,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="AP178" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS178" s="14" t="str">
@@ -13048,7 +13048,7 @@
       <c r="A179" s="6"/>
       <c r="B179" s="7"/>
       <c r="C179" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D179" s="17"/>
@@ -13067,11 +13067,11 @@
       <c r="Q179" s="17"/>
       <c r="R179" s="17"/>
       <c r="S179" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T179" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U179" s="17"/>
@@ -13090,7 +13090,7 @@
       <c r="AH179" s="17"/>
       <c r="AI179" s="17"/>
       <c r="AJ179" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK179" s="7"/>
@@ -13105,7 +13105,7 @@
         <v>0</v>
       </c>
       <c r="AP179" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS179" s="14" t="str">
@@ -13117,7 +13117,7 @@
       <c r="A180" s="15"/>
       <c r="B180" s="7"/>
       <c r="C180" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D180" s="17"/>
@@ -13136,11 +13136,11 @@
       <c r="Q180" s="17"/>
       <c r="R180" s="17"/>
       <c r="S180" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T180" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U180" s="17"/>
@@ -13159,7 +13159,7 @@
       <c r="AH180" s="17"/>
       <c r="AI180" s="17"/>
       <c r="AJ180" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK180" s="7"/>
@@ -13174,7 +13174,7 @@
         <v>0</v>
       </c>
       <c r="AP180" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS180" s="14" t="str">
@@ -13186,7 +13186,7 @@
       <c r="A181" s="6"/>
       <c r="B181" s="7"/>
       <c r="C181" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D181" s="17"/>
@@ -13205,11 +13205,11 @@
       <c r="Q181" s="17"/>
       <c r="R181" s="17"/>
       <c r="S181" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T181" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U181" s="17"/>
@@ -13228,7 +13228,7 @@
       <c r="AH181" s="17"/>
       <c r="AI181" s="17"/>
       <c r="AJ181" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK181" s="7"/>
@@ -13243,7 +13243,7 @@
         <v>0</v>
       </c>
       <c r="AP181" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS181" s="14" t="str">
@@ -13255,7 +13255,7 @@
       <c r="A182" s="15"/>
       <c r="B182" s="7"/>
       <c r="C182" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D182" s="17"/>
@@ -13274,11 +13274,11 @@
       <c r="Q182" s="17"/>
       <c r="R182" s="17"/>
       <c r="S182" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T182" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U182" s="17"/>
@@ -13297,7 +13297,7 @@
       <c r="AH182" s="17"/>
       <c r="AI182" s="17"/>
       <c r="AJ182" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK182" s="7"/>
@@ -13312,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="AP182" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS182" s="14" t="str">
@@ -13324,7 +13324,7 @@
       <c r="A183" s="6"/>
       <c r="B183" s="7"/>
       <c r="C183" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D183" s="17"/>
@@ -13343,11 +13343,11 @@
       <c r="Q183" s="17"/>
       <c r="R183" s="17"/>
       <c r="S183" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T183" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U183" s="17"/>
@@ -13366,7 +13366,7 @@
       <c r="AH183" s="17"/>
       <c r="AI183" s="17"/>
       <c r="AJ183" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK183" s="7"/>
@@ -13381,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="AP183" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS183" s="14" t="str">
@@ -13393,7 +13393,7 @@
       <c r="A184" s="15"/>
       <c r="B184" s="7"/>
       <c r="C184" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D184" s="17"/>
@@ -13412,11 +13412,11 @@
       <c r="Q184" s="17"/>
       <c r="R184" s="17"/>
       <c r="S184" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T184" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U184" s="17"/>
@@ -13435,7 +13435,7 @@
       <c r="AH184" s="17"/>
       <c r="AI184" s="17"/>
       <c r="AJ184" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK184" s="7"/>
@@ -13450,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="AP184" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS184" s="14" t="str">
@@ -13462,7 +13462,7 @@
       <c r="A185" s="6"/>
       <c r="B185" s="7"/>
       <c r="C185" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D185" s="17"/>
@@ -13481,11 +13481,11 @@
       <c r="Q185" s="17"/>
       <c r="R185" s="17"/>
       <c r="S185" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T185" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U185" s="17"/>
@@ -13504,7 +13504,7 @@
       <c r="AH185" s="17"/>
       <c r="AI185" s="17"/>
       <c r="AJ185" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK185" s="7"/>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AP185" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS185" s="14" t="str">
@@ -13531,7 +13531,7 @@
       <c r="A186" s="15"/>
       <c r="B186" s="7"/>
       <c r="C186" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D186" s="17"/>
@@ -13550,11 +13550,11 @@
       <c r="Q186" s="17"/>
       <c r="R186" s="17"/>
       <c r="S186" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T186" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U186" s="17"/>
@@ -13573,7 +13573,7 @@
       <c r="AH186" s="17"/>
       <c r="AI186" s="17"/>
       <c r="AJ186" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK186" s="7"/>
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="AP186" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS186" s="14" t="str">
@@ -13600,7 +13600,7 @@
       <c r="A187" s="6"/>
       <c r="B187" s="7"/>
       <c r="C187" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D187" s="17"/>
@@ -13619,11 +13619,11 @@
       <c r="Q187" s="17"/>
       <c r="R187" s="17"/>
       <c r="S187" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T187" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U187" s="17"/>
@@ -13642,7 +13642,7 @@
       <c r="AH187" s="17"/>
       <c r="AI187" s="17"/>
       <c r="AJ187" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK187" s="7"/>
@@ -13657,7 +13657,7 @@
         <v>0</v>
       </c>
       <c r="AP187" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS187" s="14" t="str">
@@ -13669,7 +13669,7 @@
       <c r="A188" s="15"/>
       <c r="B188" s="7"/>
       <c r="C188" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D188" s="17"/>
@@ -13688,11 +13688,11 @@
       <c r="Q188" s="17"/>
       <c r="R188" s="17"/>
       <c r="S188" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T188" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U188" s="17"/>
@@ -13711,7 +13711,7 @@
       <c r="AH188" s="17"/>
       <c r="AI188" s="17"/>
       <c r="AJ188" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK188" s="7"/>
@@ -13726,7 +13726,7 @@
         <v>0</v>
       </c>
       <c r="AP188" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS188" s="14" t="str">
@@ -13738,7 +13738,7 @@
       <c r="A189" s="6"/>
       <c r="B189" s="7"/>
       <c r="C189" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D189" s="17"/>
@@ -13757,11 +13757,11 @@
       <c r="Q189" s="17"/>
       <c r="R189" s="17"/>
       <c r="S189" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T189" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U189" s="17"/>
@@ -13780,7 +13780,7 @@
       <c r="AH189" s="17"/>
       <c r="AI189" s="17"/>
       <c r="AJ189" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK189" s="7"/>
@@ -13795,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="AP189" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS189" s="14" t="str">
@@ -13807,7 +13807,7 @@
       <c r="A190" s="15"/>
       <c r="B190" s="7"/>
       <c r="C190" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D190" s="17"/>
@@ -13826,11 +13826,11 @@
       <c r="Q190" s="17"/>
       <c r="R190" s="17"/>
       <c r="S190" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T190" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U190" s="17"/>
@@ -13849,7 +13849,7 @@
       <c r="AH190" s="17"/>
       <c r="AI190" s="17"/>
       <c r="AJ190" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK190" s="7"/>
@@ -13864,7 +13864,7 @@
         <v>0</v>
       </c>
       <c r="AP190" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS190" s="14" t="str">
@@ -13876,7 +13876,7 @@
       <c r="A191" s="6"/>
       <c r="B191" s="7"/>
       <c r="C191" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D191" s="17"/>
@@ -13895,11 +13895,11 @@
       <c r="Q191" s="17"/>
       <c r="R191" s="17"/>
       <c r="S191" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T191" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U191" s="17"/>
@@ -13918,7 +13918,7 @@
       <c r="AH191" s="17"/>
       <c r="AI191" s="17"/>
       <c r="AJ191" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK191" s="7"/>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="AP191" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS191" s="14" t="str">
@@ -13945,7 +13945,7 @@
       <c r="A192" s="15"/>
       <c r="B192" s="7"/>
       <c r="C192" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D192" s="17"/>
@@ -13964,11 +13964,11 @@
       <c r="Q192" s="17"/>
       <c r="R192" s="17"/>
       <c r="S192" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T192" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U192" s="17"/>
@@ -13987,7 +13987,7 @@
       <c r="AH192" s="17"/>
       <c r="AI192" s="17"/>
       <c r="AJ192" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK192" s="7"/>
@@ -14002,7 +14002,7 @@
         <v>0</v>
       </c>
       <c r="AP192" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS192" s="14" t="str">
@@ -14014,7 +14014,7 @@
       <c r="A193" s="6"/>
       <c r="B193" s="7"/>
       <c r="C193" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D193" s="17"/>
@@ -14033,11 +14033,11 @@
       <c r="Q193" s="17"/>
       <c r="R193" s="17"/>
       <c r="S193" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T193" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U193" s="17"/>
@@ -14056,7 +14056,7 @@
       <c r="AH193" s="17"/>
       <c r="AI193" s="17"/>
       <c r="AJ193" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK193" s="7"/>
@@ -14071,7 +14071,7 @@
         <v>0</v>
       </c>
       <c r="AP193" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS193" s="14" t="str">
@@ -14083,7 +14083,7 @@
       <c r="A194" s="15"/>
       <c r="B194" s="7"/>
       <c r="C194" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D194" s="17"/>
@@ -14102,11 +14102,11 @@
       <c r="Q194" s="17"/>
       <c r="R194" s="17"/>
       <c r="S194" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T194" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U194" s="17"/>
@@ -14125,7 +14125,7 @@
       <c r="AH194" s="17"/>
       <c r="AI194" s="17"/>
       <c r="AJ194" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK194" s="7"/>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="AP194" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS194" s="14" t="str">
@@ -14152,7 +14152,7 @@
       <c r="A195" s="6"/>
       <c r="B195" s="7"/>
       <c r="C195" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D195" s="17"/>
@@ -14171,11 +14171,11 @@
       <c r="Q195" s="17"/>
       <c r="R195" s="17"/>
       <c r="S195" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T195" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U195" s="17"/>
@@ -14194,7 +14194,7 @@
       <c r="AH195" s="17"/>
       <c r="AI195" s="17"/>
       <c r="AJ195" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK195" s="7"/>
@@ -14209,7 +14209,7 @@
         <v>0</v>
       </c>
       <c r="AP195" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS195" s="14" t="str">
@@ -14221,7 +14221,7 @@
       <c r="A196" s="15"/>
       <c r="B196" s="7"/>
       <c r="C196" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D196" s="17"/>
@@ -14240,11 +14240,11 @@
       <c r="Q196" s="17"/>
       <c r="R196" s="17"/>
       <c r="S196" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T196" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U196" s="17"/>
@@ -14263,7 +14263,7 @@
       <c r="AH196" s="17"/>
       <c r="AI196" s="17"/>
       <c r="AJ196" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK196" s="7"/>
@@ -14278,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="AP196" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS196" s="14" t="str">
@@ -14290,7 +14290,7 @@
       <c r="A197" s="6"/>
       <c r="B197" s="7"/>
       <c r="C197" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="D197" s="17"/>
@@ -14309,11 +14309,11 @@
       <c r="Q197" s="17"/>
       <c r="R197" s="17"/>
       <c r="S197" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="T197" s="8" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U197" s="17"/>
@@ -14332,7 +14332,7 @@
       <c r="AH197" s="17"/>
       <c r="AI197" s="17"/>
       <c r="AJ197" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK197" s="7"/>
@@ -14347,7 +14347,7 @@
         <v>0</v>
       </c>
       <c r="AP197" s="13" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS197" s="14" t="str">
@@ -14359,7 +14359,7 @@
       <c r="A198" s="15"/>
       <c r="B198" s="7"/>
       <c r="C198" s="8" t="str">
-        <f t="shared" ref="C198:C261" si="16">IF(COUNTA($D$3:$R$3)=0, "", COUNTA($D$3:$R$3))</f>
+        <f t="shared" ref="C198:C261" si="18">IF(COUNTA($D$3:$R$3)=0, "", COUNTA($D$3:$R$3))</f>
         <v/>
       </c>
       <c r="D198" s="17"/>
@@ -14378,11 +14378,11 @@
       <c r="Q198" s="17"/>
       <c r="R198" s="17"/>
       <c r="S198" s="9">
-        <f t="shared" ref="S198:S261" si="17">IFERROR(ROUND(SUM(D198,E198,F198,G198,H198,I198,J198,K198,L198,M198,N198,O198,P198,Q198,R198)/C198*20,0),0)</f>
+        <f t="shared" ref="S198:S261" si="19">IFERROR(ROUND(SUM(D198,E198,F198,G198,H198,I198,J198,K198,L198,M198,N198,O198,P198,Q198,R198)/C198*20,0),0)</f>
         <v>0</v>
       </c>
       <c r="T198" s="8" t="str">
-        <f t="shared" ref="T198:T261" si="18">IF(COUNTA($U$3:$AI$3 )=0, "", COUNTA($U$3:$AI$3))</f>
+        <f t="shared" ref="T198:T261" si="20">IF(COUNTA($U$3:$AI$3 )=0, "", COUNTA($U$3:$AI$3))</f>
         <v/>
       </c>
       <c r="U198" s="17"/>
@@ -14401,7 +14401,7 @@
       <c r="AH198" s="17"/>
       <c r="AI198" s="17"/>
       <c r="AJ198" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AJ198:AJ261" si="21">IFERROR(ROUND(SUM(AI198,AH198,AG198,AF198,AE198,AD198,AC198,AB198,AA198,Z198,Y198,X198,W198,V198,U198,)/T198*10,0),0)</f>
         <v>0</v>
       </c>
       <c r="AK198" s="7"/>
@@ -14416,7 +14416,7 @@
         <v>0</v>
       </c>
       <c r="AP198" s="13" t="str">
-        <f t="shared" ref="AP198:AP261" si="19">IF(AN198&gt;=90,"A",IF(AN198&gt;=80,"B",IF(AN198&gt;=70,"C",IF(AN198&gt;=60,"D",IF(AN198&gt;0,"F"," ")))))</f>
+        <f t="shared" ref="AP198:AP261" si="22">IF(AN198&gt;=90,"A",IF(AN198&gt;=80,"B",IF(AN198&gt;=70,"C",IF(AN198&gt;=60,"D",IF(AN198&gt;0,"F"," ")))))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS198" s="14" t="str">
@@ -14428,7 +14428,7 @@
       <c r="A199" s="6"/>
       <c r="B199" s="7"/>
       <c r="C199" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D199" s="17"/>
@@ -14447,11 +14447,11 @@
       <c r="Q199" s="17"/>
       <c r="R199" s="17"/>
       <c r="S199" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T199" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U199" s="17"/>
@@ -14470,7 +14470,7 @@
       <c r="AH199" s="17"/>
       <c r="AI199" s="17"/>
       <c r="AJ199" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK199" s="7"/>
@@ -14485,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="AP199" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS199" s="14" t="str">
@@ -14497,7 +14497,7 @@
       <c r="A200" s="15"/>
       <c r="B200" s="7"/>
       <c r="C200" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D200" s="17"/>
@@ -14516,11 +14516,11 @@
       <c r="Q200" s="17"/>
       <c r="R200" s="17"/>
       <c r="S200" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T200" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U200" s="17"/>
@@ -14539,7 +14539,7 @@
       <c r="AH200" s="17"/>
       <c r="AI200" s="17"/>
       <c r="AJ200" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK200" s="7"/>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="AP200" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS200" s="14" t="str">
@@ -14566,7 +14566,7 @@
       <c r="A201" s="6"/>
       <c r="B201" s="7"/>
       <c r="C201" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D201" s="17"/>
@@ -14585,11 +14585,11 @@
       <c r="Q201" s="17"/>
       <c r="R201" s="17"/>
       <c r="S201" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T201" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U201" s="17"/>
@@ -14608,7 +14608,7 @@
       <c r="AH201" s="17"/>
       <c r="AI201" s="17"/>
       <c r="AJ201" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK201" s="7"/>
@@ -14623,7 +14623,7 @@
         <v>0</v>
       </c>
       <c r="AP201" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS201" s="14" t="str">
@@ -14635,7 +14635,7 @@
       <c r="A202" s="15"/>
       <c r="B202" s="7"/>
       <c r="C202" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D202" s="17"/>
@@ -14654,11 +14654,11 @@
       <c r="Q202" s="17"/>
       <c r="R202" s="17"/>
       <c r="S202" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T202" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U202" s="17"/>
@@ -14677,7 +14677,7 @@
       <c r="AH202" s="17"/>
       <c r="AI202" s="17"/>
       <c r="AJ202" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK202" s="7"/>
@@ -14692,7 +14692,7 @@
         <v>0</v>
       </c>
       <c r="AP202" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS202" s="14" t="str">
@@ -14704,7 +14704,7 @@
       <c r="A203" s="6"/>
       <c r="B203" s="7"/>
       <c r="C203" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D203" s="17"/>
@@ -14723,11 +14723,11 @@
       <c r="Q203" s="17"/>
       <c r="R203" s="17"/>
       <c r="S203" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T203" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U203" s="17"/>
@@ -14746,7 +14746,7 @@
       <c r="AH203" s="17"/>
       <c r="AI203" s="17"/>
       <c r="AJ203" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK203" s="7"/>
@@ -14761,7 +14761,7 @@
         <v>0</v>
       </c>
       <c r="AP203" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS203" s="14" t="str">
@@ -14773,7 +14773,7 @@
       <c r="A204" s="15"/>
       <c r="B204" s="7"/>
       <c r="C204" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D204" s="17"/>
@@ -14792,11 +14792,11 @@
       <c r="Q204" s="17"/>
       <c r="R204" s="17"/>
       <c r="S204" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T204" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U204" s="17"/>
@@ -14815,7 +14815,7 @@
       <c r="AH204" s="17"/>
       <c r="AI204" s="17"/>
       <c r="AJ204" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK204" s="7"/>
@@ -14830,7 +14830,7 @@
         <v>0</v>
       </c>
       <c r="AP204" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS204" s="14" t="str">
@@ -14842,7 +14842,7 @@
       <c r="A205" s="6"/>
       <c r="B205" s="7"/>
       <c r="C205" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D205" s="17"/>
@@ -14861,11 +14861,11 @@
       <c r="Q205" s="17"/>
       <c r="R205" s="17"/>
       <c r="S205" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T205" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U205" s="17"/>
@@ -14884,7 +14884,7 @@
       <c r="AH205" s="17"/>
       <c r="AI205" s="17"/>
       <c r="AJ205" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK205" s="7"/>
@@ -14899,7 +14899,7 @@
         <v>0</v>
       </c>
       <c r="AP205" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS205" s="14" t="str">
@@ -14911,7 +14911,7 @@
       <c r="A206" s="15"/>
       <c r="B206" s="7"/>
       <c r="C206" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D206" s="17"/>
@@ -14930,11 +14930,11 @@
       <c r="Q206" s="17"/>
       <c r="R206" s="17"/>
       <c r="S206" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T206" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U206" s="17"/>
@@ -14953,7 +14953,7 @@
       <c r="AH206" s="17"/>
       <c r="AI206" s="17"/>
       <c r="AJ206" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK206" s="7"/>
@@ -14968,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="AP206" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS206" s="14" t="str">
@@ -14980,7 +14980,7 @@
       <c r="A207" s="6"/>
       <c r="B207" s="7"/>
       <c r="C207" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D207" s="17"/>
@@ -14999,11 +14999,11 @@
       <c r="Q207" s="17"/>
       <c r="R207" s="17"/>
       <c r="S207" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T207" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U207" s="17"/>
@@ -15022,7 +15022,7 @@
       <c r="AH207" s="17"/>
       <c r="AI207" s="17"/>
       <c r="AJ207" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK207" s="7"/>
@@ -15037,7 +15037,7 @@
         <v>0</v>
       </c>
       <c r="AP207" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS207" s="14" t="str">
@@ -15049,7 +15049,7 @@
       <c r="A208" s="15"/>
       <c r="B208" s="7"/>
       <c r="C208" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D208" s="17"/>
@@ -15068,11 +15068,11 @@
       <c r="Q208" s="17"/>
       <c r="R208" s="17"/>
       <c r="S208" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T208" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U208" s="17"/>
@@ -15091,7 +15091,7 @@
       <c r="AH208" s="17"/>
       <c r="AI208" s="17"/>
       <c r="AJ208" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK208" s="7"/>
@@ -15106,7 +15106,7 @@
         <v>0</v>
       </c>
       <c r="AP208" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS208" s="14" t="str">
@@ -15118,7 +15118,7 @@
       <c r="A209" s="6"/>
       <c r="B209" s="7"/>
       <c r="C209" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D209" s="17"/>
@@ -15137,11 +15137,11 @@
       <c r="Q209" s="17"/>
       <c r="R209" s="17"/>
       <c r="S209" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T209" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U209" s="17"/>
@@ -15160,7 +15160,7 @@
       <c r="AH209" s="17"/>
       <c r="AI209" s="17"/>
       <c r="AJ209" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK209" s="7"/>
@@ -15175,7 +15175,7 @@
         <v>0</v>
       </c>
       <c r="AP209" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS209" s="14" t="str">
@@ -15187,7 +15187,7 @@
       <c r="A210" s="15"/>
       <c r="B210" s="7"/>
       <c r="C210" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D210" s="17"/>
@@ -15206,11 +15206,11 @@
       <c r="Q210" s="17"/>
       <c r="R210" s="17"/>
       <c r="S210" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T210" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U210" s="17"/>
@@ -15229,7 +15229,7 @@
       <c r="AH210" s="17"/>
       <c r="AI210" s="17"/>
       <c r="AJ210" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK210" s="7"/>
@@ -15244,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="AP210" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS210" s="14" t="str">
@@ -15256,7 +15256,7 @@
       <c r="A211" s="6"/>
       <c r="B211" s="7"/>
       <c r="C211" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D211" s="17"/>
@@ -15275,11 +15275,11 @@
       <c r="Q211" s="17"/>
       <c r="R211" s="17"/>
       <c r="S211" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T211" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U211" s="17"/>
@@ -15298,7 +15298,7 @@
       <c r="AH211" s="17"/>
       <c r="AI211" s="17"/>
       <c r="AJ211" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK211" s="7"/>
@@ -15313,7 +15313,7 @@
         <v>0</v>
       </c>
       <c r="AP211" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS211" s="14" t="str">
@@ -15325,7 +15325,7 @@
       <c r="A212" s="15"/>
       <c r="B212" s="7"/>
       <c r="C212" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D212" s="17"/>
@@ -15344,11 +15344,11 @@
       <c r="Q212" s="17"/>
       <c r="R212" s="17"/>
       <c r="S212" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T212" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U212" s="17"/>
@@ -15367,7 +15367,7 @@
       <c r="AH212" s="17"/>
       <c r="AI212" s="17"/>
       <c r="AJ212" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK212" s="7"/>
@@ -15382,7 +15382,7 @@
         <v>0</v>
       </c>
       <c r="AP212" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS212" s="14" t="str">
@@ -15394,7 +15394,7 @@
       <c r="A213" s="6"/>
       <c r="B213" s="7"/>
       <c r="C213" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D213" s="17"/>
@@ -15413,11 +15413,11 @@
       <c r="Q213" s="17"/>
       <c r="R213" s="17"/>
       <c r="S213" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T213" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U213" s="17"/>
@@ -15436,7 +15436,7 @@
       <c r="AH213" s="17"/>
       <c r="AI213" s="17"/>
       <c r="AJ213" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK213" s="7"/>
@@ -15451,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="AP213" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS213" s="14" t="str">
@@ -15463,7 +15463,7 @@
       <c r="A214" s="15"/>
       <c r="B214" s="7"/>
       <c r="C214" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D214" s="17"/>
@@ -15482,11 +15482,11 @@
       <c r="Q214" s="17"/>
       <c r="R214" s="17"/>
       <c r="S214" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T214" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U214" s="17"/>
@@ -15505,7 +15505,7 @@
       <c r="AH214" s="17"/>
       <c r="AI214" s="17"/>
       <c r="AJ214" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK214" s="7"/>
@@ -15520,7 +15520,7 @@
         <v>0</v>
       </c>
       <c r="AP214" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS214" s="14" t="str">
@@ -15532,7 +15532,7 @@
       <c r="A215" s="6"/>
       <c r="B215" s="7"/>
       <c r="C215" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D215" s="17"/>
@@ -15551,11 +15551,11 @@
       <c r="Q215" s="17"/>
       <c r="R215" s="17"/>
       <c r="S215" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T215" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U215" s="17"/>
@@ -15574,7 +15574,7 @@
       <c r="AH215" s="17"/>
       <c r="AI215" s="17"/>
       <c r="AJ215" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK215" s="7"/>
@@ -15589,7 +15589,7 @@
         <v>0</v>
       </c>
       <c r="AP215" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS215" s="14" t="str">
@@ -15601,7 +15601,7 @@
       <c r="A216" s="15"/>
       <c r="B216" s="7"/>
       <c r="C216" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D216" s="17"/>
@@ -15620,11 +15620,11 @@
       <c r="Q216" s="17"/>
       <c r="R216" s="17"/>
       <c r="S216" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T216" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U216" s="17"/>
@@ -15643,7 +15643,7 @@
       <c r="AH216" s="17"/>
       <c r="AI216" s="17"/>
       <c r="AJ216" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK216" s="7"/>
@@ -15658,7 +15658,7 @@
         <v>0</v>
       </c>
       <c r="AP216" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS216" s="14" t="str">
@@ -15670,7 +15670,7 @@
       <c r="A217" s="6"/>
       <c r="B217" s="7"/>
       <c r="C217" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D217" s="17"/>
@@ -15689,11 +15689,11 @@
       <c r="Q217" s="17"/>
       <c r="R217" s="17"/>
       <c r="S217" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T217" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U217" s="17"/>
@@ -15712,7 +15712,7 @@
       <c r="AH217" s="17"/>
       <c r="AI217" s="17"/>
       <c r="AJ217" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK217" s="7"/>
@@ -15727,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="AP217" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS217" s="14" t="str">
@@ -15739,7 +15739,7 @@
       <c r="A218" s="15"/>
       <c r="B218" s="7"/>
       <c r="C218" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D218" s="17"/>
@@ -15758,11 +15758,11 @@
       <c r="Q218" s="17"/>
       <c r="R218" s="17"/>
       <c r="S218" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T218" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U218" s="17"/>
@@ -15781,7 +15781,7 @@
       <c r="AH218" s="17"/>
       <c r="AI218" s="17"/>
       <c r="AJ218" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK218" s="7"/>
@@ -15796,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="AP218" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS218" s="14" t="str">
@@ -15808,7 +15808,7 @@
       <c r="A219" s="6"/>
       <c r="B219" s="7"/>
       <c r="C219" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D219" s="17"/>
@@ -15827,11 +15827,11 @@
       <c r="Q219" s="17"/>
       <c r="R219" s="17"/>
       <c r="S219" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T219" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U219" s="17"/>
@@ -15850,7 +15850,7 @@
       <c r="AH219" s="17"/>
       <c r="AI219" s="17"/>
       <c r="AJ219" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK219" s="7"/>
@@ -15865,7 +15865,7 @@
         <v>0</v>
       </c>
       <c r="AP219" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS219" s="14" t="str">
@@ -15877,7 +15877,7 @@
       <c r="A220" s="15"/>
       <c r="B220" s="7"/>
       <c r="C220" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D220" s="17"/>
@@ -15896,11 +15896,11 @@
       <c r="Q220" s="17"/>
       <c r="R220" s="17"/>
       <c r="S220" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T220" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U220" s="17"/>
@@ -15919,7 +15919,7 @@
       <c r="AH220" s="17"/>
       <c r="AI220" s="17"/>
       <c r="AJ220" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK220" s="7"/>
@@ -15934,7 +15934,7 @@
         <v>0</v>
       </c>
       <c r="AP220" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS220" s="14" t="str">
@@ -15946,7 +15946,7 @@
       <c r="A221" s="6"/>
       <c r="B221" s="7"/>
       <c r="C221" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D221" s="17"/>
@@ -15965,11 +15965,11 @@
       <c r="Q221" s="17"/>
       <c r="R221" s="17"/>
       <c r="S221" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T221" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U221" s="17"/>
@@ -15988,7 +15988,7 @@
       <c r="AH221" s="17"/>
       <c r="AI221" s="17"/>
       <c r="AJ221" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK221" s="7"/>
@@ -16003,7 +16003,7 @@
         <v>0</v>
       </c>
       <c r="AP221" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS221" s="14" t="str">
@@ -16015,7 +16015,7 @@
       <c r="A222" s="15"/>
       <c r="B222" s="7"/>
       <c r="C222" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D222" s="17"/>
@@ -16034,11 +16034,11 @@
       <c r="Q222" s="17"/>
       <c r="R222" s="17"/>
       <c r="S222" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T222" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U222" s="17"/>
@@ -16057,7 +16057,7 @@
       <c r="AH222" s="17"/>
       <c r="AI222" s="17"/>
       <c r="AJ222" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK222" s="7"/>
@@ -16072,7 +16072,7 @@
         <v>0</v>
       </c>
       <c r="AP222" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS222" s="14" t="str">
@@ -16084,7 +16084,7 @@
       <c r="A223" s="6"/>
       <c r="B223" s="7"/>
       <c r="C223" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D223" s="17"/>
@@ -16103,11 +16103,11 @@
       <c r="Q223" s="17"/>
       <c r="R223" s="17"/>
       <c r="S223" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T223" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U223" s="17"/>
@@ -16126,7 +16126,7 @@
       <c r="AH223" s="17"/>
       <c r="AI223" s="17"/>
       <c r="AJ223" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK223" s="7"/>
@@ -16141,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="AP223" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS223" s="14" t="str">
@@ -16153,7 +16153,7 @@
       <c r="A224" s="15"/>
       <c r="B224" s="7"/>
       <c r="C224" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D224" s="17"/>
@@ -16172,11 +16172,11 @@
       <c r="Q224" s="17"/>
       <c r="R224" s="17"/>
       <c r="S224" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T224" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U224" s="17"/>
@@ -16195,7 +16195,7 @@
       <c r="AH224" s="17"/>
       <c r="AI224" s="17"/>
       <c r="AJ224" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK224" s="7"/>
@@ -16210,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="AP224" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS224" s="14" t="str">
@@ -16222,7 +16222,7 @@
       <c r="A225" s="6"/>
       <c r="B225" s="7"/>
       <c r="C225" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D225" s="17"/>
@@ -16241,11 +16241,11 @@
       <c r="Q225" s="17"/>
       <c r="R225" s="17"/>
       <c r="S225" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T225" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U225" s="17"/>
@@ -16264,7 +16264,7 @@
       <c r="AH225" s="17"/>
       <c r="AI225" s="17"/>
       <c r="AJ225" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK225" s="7"/>
@@ -16279,7 +16279,7 @@
         <v>0</v>
       </c>
       <c r="AP225" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS225" s="14" t="str">
@@ -16291,7 +16291,7 @@
       <c r="A226" s="15"/>
       <c r="B226" s="7"/>
       <c r="C226" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D226" s="17"/>
@@ -16310,11 +16310,11 @@
       <c r="Q226" s="17"/>
       <c r="R226" s="17"/>
       <c r="S226" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T226" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U226" s="17"/>
@@ -16333,7 +16333,7 @@
       <c r="AH226" s="17"/>
       <c r="AI226" s="17"/>
       <c r="AJ226" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK226" s="7"/>
@@ -16348,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="AP226" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS226" s="14" t="str">
@@ -16360,7 +16360,7 @@
       <c r="A227" s="6"/>
       <c r="B227" s="7"/>
       <c r="C227" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D227" s="17"/>
@@ -16379,11 +16379,11 @@
       <c r="Q227" s="17"/>
       <c r="R227" s="17"/>
       <c r="S227" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T227" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U227" s="17"/>
@@ -16402,7 +16402,7 @@
       <c r="AH227" s="17"/>
       <c r="AI227" s="17"/>
       <c r="AJ227" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK227" s="7"/>
@@ -16417,7 +16417,7 @@
         <v>0</v>
       </c>
       <c r="AP227" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS227" s="14" t="str">
@@ -16429,7 +16429,7 @@
       <c r="A228" s="15"/>
       <c r="B228" s="7"/>
       <c r="C228" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D228" s="17"/>
@@ -16448,11 +16448,11 @@
       <c r="Q228" s="17"/>
       <c r="R228" s="17"/>
       <c r="S228" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T228" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U228" s="17"/>
@@ -16471,7 +16471,7 @@
       <c r="AH228" s="17"/>
       <c r="AI228" s="17"/>
       <c r="AJ228" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK228" s="7"/>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AP228" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS228" s="14" t="str">
@@ -16498,7 +16498,7 @@
       <c r="A229" s="6"/>
       <c r="B229" s="7"/>
       <c r="C229" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D229" s="17"/>
@@ -16517,11 +16517,11 @@
       <c r="Q229" s="17"/>
       <c r="R229" s="17"/>
       <c r="S229" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T229" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U229" s="17"/>
@@ -16540,7 +16540,7 @@
       <c r="AH229" s="17"/>
       <c r="AI229" s="17"/>
       <c r="AJ229" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK229" s="7"/>
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AP229" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS229" s="14" t="str">
@@ -16567,7 +16567,7 @@
       <c r="A230" s="15"/>
       <c r="B230" s="7"/>
       <c r="C230" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D230" s="17"/>
@@ -16586,11 +16586,11 @@
       <c r="Q230" s="17"/>
       <c r="R230" s="17"/>
       <c r="S230" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T230" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U230" s="17"/>
@@ -16609,7 +16609,7 @@
       <c r="AH230" s="17"/>
       <c r="AI230" s="17"/>
       <c r="AJ230" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK230" s="7"/>
@@ -16624,7 +16624,7 @@
         <v>0</v>
       </c>
       <c r="AP230" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS230" s="14" t="str">
@@ -16636,7 +16636,7 @@
       <c r="A231" s="6"/>
       <c r="B231" s="7"/>
       <c r="C231" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D231" s="17"/>
@@ -16655,11 +16655,11 @@
       <c r="Q231" s="17"/>
       <c r="R231" s="17"/>
       <c r="S231" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T231" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U231" s="17"/>
@@ -16678,7 +16678,7 @@
       <c r="AH231" s="17"/>
       <c r="AI231" s="17"/>
       <c r="AJ231" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK231" s="7"/>
@@ -16693,7 +16693,7 @@
         <v>0</v>
       </c>
       <c r="AP231" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS231" s="14" t="str">
@@ -16705,7 +16705,7 @@
       <c r="A232" s="15"/>
       <c r="B232" s="7"/>
       <c r="C232" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D232" s="17"/>
@@ -16724,11 +16724,11 @@
       <c r="Q232" s="17"/>
       <c r="R232" s="17"/>
       <c r="S232" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T232" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U232" s="17"/>
@@ -16747,7 +16747,7 @@
       <c r="AH232" s="17"/>
       <c r="AI232" s="17"/>
       <c r="AJ232" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK232" s="7"/>
@@ -16762,7 +16762,7 @@
         <v>0</v>
       </c>
       <c r="AP232" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS232" s="14" t="str">
@@ -16774,7 +16774,7 @@
       <c r="A233" s="6"/>
       <c r="B233" s="7"/>
       <c r="C233" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D233" s="17"/>
@@ -16793,11 +16793,11 @@
       <c r="Q233" s="17"/>
       <c r="R233" s="17"/>
       <c r="S233" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T233" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U233" s="17"/>
@@ -16816,7 +16816,7 @@
       <c r="AH233" s="17"/>
       <c r="AI233" s="17"/>
       <c r="AJ233" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK233" s="7"/>
@@ -16831,7 +16831,7 @@
         <v>0</v>
       </c>
       <c r="AP233" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS233" s="14" t="str">
@@ -16843,7 +16843,7 @@
       <c r="A234" s="15"/>
       <c r="B234" s="7"/>
       <c r="C234" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D234" s="17"/>
@@ -16862,11 +16862,11 @@
       <c r="Q234" s="17"/>
       <c r="R234" s="17"/>
       <c r="S234" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T234" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U234" s="17"/>
@@ -16885,7 +16885,7 @@
       <c r="AH234" s="17"/>
       <c r="AI234" s="17"/>
       <c r="AJ234" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK234" s="7"/>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="AP234" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS234" s="14" t="str">
@@ -16912,7 +16912,7 @@
       <c r="A235" s="6"/>
       <c r="B235" s="7"/>
       <c r="C235" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D235" s="17"/>
@@ -16931,11 +16931,11 @@
       <c r="Q235" s="17"/>
       <c r="R235" s="17"/>
       <c r="S235" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T235" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U235" s="17"/>
@@ -16954,7 +16954,7 @@
       <c r="AH235" s="17"/>
       <c r="AI235" s="17"/>
       <c r="AJ235" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK235" s="7"/>
@@ -16969,7 +16969,7 @@
         <v>0</v>
       </c>
       <c r="AP235" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS235" s="14" t="str">
@@ -16981,7 +16981,7 @@
       <c r="A236" s="15"/>
       <c r="B236" s="7"/>
       <c r="C236" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D236" s="17"/>
@@ -17000,11 +17000,11 @@
       <c r="Q236" s="17"/>
       <c r="R236" s="17"/>
       <c r="S236" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T236" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U236" s="17"/>
@@ -17023,7 +17023,7 @@
       <c r="AH236" s="17"/>
       <c r="AI236" s="17"/>
       <c r="AJ236" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK236" s="7"/>
@@ -17038,7 +17038,7 @@
         <v>0</v>
       </c>
       <c r="AP236" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS236" s="14" t="str">
@@ -17050,7 +17050,7 @@
       <c r="A237" s="6"/>
       <c r="B237" s="7"/>
       <c r="C237" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D237" s="17"/>
@@ -17069,11 +17069,11 @@
       <c r="Q237" s="17"/>
       <c r="R237" s="17"/>
       <c r="S237" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T237" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U237" s="17"/>
@@ -17092,7 +17092,7 @@
       <c r="AH237" s="17"/>
       <c r="AI237" s="17"/>
       <c r="AJ237" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK237" s="7"/>
@@ -17107,7 +17107,7 @@
         <v>0</v>
       </c>
       <c r="AP237" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS237" s="14" t="str">
@@ -17119,7 +17119,7 @@
       <c r="A238" s="15"/>
       <c r="B238" s="7"/>
       <c r="C238" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D238" s="17"/>
@@ -17138,11 +17138,11 @@
       <c r="Q238" s="17"/>
       <c r="R238" s="17"/>
       <c r="S238" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T238" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U238" s="17"/>
@@ -17161,7 +17161,7 @@
       <c r="AH238" s="17"/>
       <c r="AI238" s="17"/>
       <c r="AJ238" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK238" s="7"/>
@@ -17176,7 +17176,7 @@
         <v>0</v>
       </c>
       <c r="AP238" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS238" s="14" t="str">
@@ -17188,7 +17188,7 @@
       <c r="A239" s="6"/>
       <c r="B239" s="7"/>
       <c r="C239" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D239" s="17"/>
@@ -17207,11 +17207,11 @@
       <c r="Q239" s="17"/>
       <c r="R239" s="17"/>
       <c r="S239" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T239" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U239" s="17"/>
@@ -17230,7 +17230,7 @@
       <c r="AH239" s="17"/>
       <c r="AI239" s="17"/>
       <c r="AJ239" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK239" s="7"/>
@@ -17245,7 +17245,7 @@
         <v>0</v>
       </c>
       <c r="AP239" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS239" s="14" t="str">
@@ -17257,7 +17257,7 @@
       <c r="A240" s="15"/>
       <c r="B240" s="7"/>
       <c r="C240" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D240" s="17"/>
@@ -17276,11 +17276,11 @@
       <c r="Q240" s="17"/>
       <c r="R240" s="17"/>
       <c r="S240" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T240" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U240" s="17"/>
@@ -17299,7 +17299,7 @@
       <c r="AH240" s="17"/>
       <c r="AI240" s="17"/>
       <c r="AJ240" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK240" s="7"/>
@@ -17314,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="AP240" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS240" s="14" t="str">
@@ -17326,7 +17326,7 @@
       <c r="A241" s="6"/>
       <c r="B241" s="7"/>
       <c r="C241" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D241" s="17"/>
@@ -17345,11 +17345,11 @@
       <c r="Q241" s="17"/>
       <c r="R241" s="17"/>
       <c r="S241" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T241" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U241" s="17"/>
@@ -17368,7 +17368,7 @@
       <c r="AH241" s="17"/>
       <c r="AI241" s="17"/>
       <c r="AJ241" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK241" s="7"/>
@@ -17383,7 +17383,7 @@
         <v>0</v>
       </c>
       <c r="AP241" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS241" s="14" t="str">
@@ -17395,7 +17395,7 @@
       <c r="A242" s="15"/>
       <c r="B242" s="7"/>
       <c r="C242" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D242" s="17"/>
@@ -17414,11 +17414,11 @@
       <c r="Q242" s="17"/>
       <c r="R242" s="17"/>
       <c r="S242" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T242" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U242" s="17"/>
@@ -17437,7 +17437,7 @@
       <c r="AH242" s="17"/>
       <c r="AI242" s="17"/>
       <c r="AJ242" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK242" s="7"/>
@@ -17452,7 +17452,7 @@
         <v>0</v>
       </c>
       <c r="AP242" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS242" s="14" t="str">
@@ -17464,7 +17464,7 @@
       <c r="A243" s="6"/>
       <c r="B243" s="7"/>
       <c r="C243" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D243" s="17"/>
@@ -17483,11 +17483,11 @@
       <c r="Q243" s="17"/>
       <c r="R243" s="17"/>
       <c r="S243" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T243" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U243" s="17"/>
@@ -17506,7 +17506,7 @@
       <c r="AH243" s="17"/>
       <c r="AI243" s="17"/>
       <c r="AJ243" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK243" s="7"/>
@@ -17521,7 +17521,7 @@
         <v>0</v>
       </c>
       <c r="AP243" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS243" s="14" t="str">
@@ -17533,7 +17533,7 @@
       <c r="A244" s="15"/>
       <c r="B244" s="7"/>
       <c r="C244" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D244" s="17"/>
@@ -17552,11 +17552,11 @@
       <c r="Q244" s="17"/>
       <c r="R244" s="17"/>
       <c r="S244" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T244" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U244" s="17"/>
@@ -17575,7 +17575,7 @@
       <c r="AH244" s="17"/>
       <c r="AI244" s="17"/>
       <c r="AJ244" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK244" s="7"/>
@@ -17590,7 +17590,7 @@
         <v>0</v>
       </c>
       <c r="AP244" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS244" s="14" t="str">
@@ -17602,7 +17602,7 @@
       <c r="A245" s="6"/>
       <c r="B245" s="7"/>
       <c r="C245" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D245" s="17"/>
@@ -17621,11 +17621,11 @@
       <c r="Q245" s="17"/>
       <c r="R245" s="17"/>
       <c r="S245" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T245" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U245" s="17"/>
@@ -17644,7 +17644,7 @@
       <c r="AH245" s="17"/>
       <c r="AI245" s="17"/>
       <c r="AJ245" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK245" s="7"/>
@@ -17659,7 +17659,7 @@
         <v>0</v>
       </c>
       <c r="AP245" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS245" s="14" t="str">
@@ -17671,7 +17671,7 @@
       <c r="A246" s="15"/>
       <c r="B246" s="7"/>
       <c r="C246" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D246" s="17"/>
@@ -17690,11 +17690,11 @@
       <c r="Q246" s="17"/>
       <c r="R246" s="17"/>
       <c r="S246" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T246" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U246" s="17"/>
@@ -17713,7 +17713,7 @@
       <c r="AH246" s="17"/>
       <c r="AI246" s="17"/>
       <c r="AJ246" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK246" s="7"/>
@@ -17728,7 +17728,7 @@
         <v>0</v>
       </c>
       <c r="AP246" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS246" s="14" t="str">
@@ -17740,7 +17740,7 @@
       <c r="A247" s="6"/>
       <c r="B247" s="7"/>
       <c r="C247" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D247" s="17"/>
@@ -17759,11 +17759,11 @@
       <c r="Q247" s="17"/>
       <c r="R247" s="17"/>
       <c r="S247" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T247" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U247" s="17"/>
@@ -17782,7 +17782,7 @@
       <c r="AH247" s="17"/>
       <c r="AI247" s="17"/>
       <c r="AJ247" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK247" s="7"/>
@@ -17797,7 +17797,7 @@
         <v>0</v>
       </c>
       <c r="AP247" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS247" s="14" t="str">
@@ -17809,7 +17809,7 @@
       <c r="A248" s="15"/>
       <c r="B248" s="7"/>
       <c r="C248" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D248" s="17"/>
@@ -17828,11 +17828,11 @@
       <c r="Q248" s="17"/>
       <c r="R248" s="17"/>
       <c r="S248" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T248" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U248" s="17"/>
@@ -17851,7 +17851,7 @@
       <c r="AH248" s="17"/>
       <c r="AI248" s="17"/>
       <c r="AJ248" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK248" s="7"/>
@@ -17866,7 +17866,7 @@
         <v>0</v>
       </c>
       <c r="AP248" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS248" s="14" t="str">
@@ -17878,7 +17878,7 @@
       <c r="A249" s="6"/>
       <c r="B249" s="7"/>
       <c r="C249" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D249" s="17"/>
@@ -17897,11 +17897,11 @@
       <c r="Q249" s="17"/>
       <c r="R249" s="17"/>
       <c r="S249" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T249" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U249" s="17"/>
@@ -17920,7 +17920,7 @@
       <c r="AH249" s="17"/>
       <c r="AI249" s="17"/>
       <c r="AJ249" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK249" s="7"/>
@@ -17935,7 +17935,7 @@
         <v>0</v>
       </c>
       <c r="AP249" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS249" s="14" t="str">
@@ -17947,7 +17947,7 @@
       <c r="A250" s="15"/>
       <c r="B250" s="7"/>
       <c r="C250" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D250" s="17"/>
@@ -17966,11 +17966,11 @@
       <c r="Q250" s="17"/>
       <c r="R250" s="17"/>
       <c r="S250" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T250" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U250" s="17"/>
@@ -17989,7 +17989,7 @@
       <c r="AH250" s="17"/>
       <c r="AI250" s="17"/>
       <c r="AJ250" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK250" s="7"/>
@@ -18004,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="AP250" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS250" s="14" t="str">
@@ -18016,7 +18016,7 @@
       <c r="A251" s="6"/>
       <c r="B251" s="7"/>
       <c r="C251" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D251" s="17"/>
@@ -18035,11 +18035,11 @@
       <c r="Q251" s="17"/>
       <c r="R251" s="17"/>
       <c r="S251" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T251" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U251" s="17"/>
@@ -18058,7 +18058,7 @@
       <c r="AH251" s="17"/>
       <c r="AI251" s="17"/>
       <c r="AJ251" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK251" s="7"/>
@@ -18073,7 +18073,7 @@
         <v>0</v>
       </c>
       <c r="AP251" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS251" s="14" t="str">
@@ -18085,7 +18085,7 @@
       <c r="A252" s="15"/>
       <c r="B252" s="7"/>
       <c r="C252" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D252" s="17"/>
@@ -18104,11 +18104,11 @@
       <c r="Q252" s="17"/>
       <c r="R252" s="17"/>
       <c r="S252" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T252" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U252" s="17"/>
@@ -18127,7 +18127,7 @@
       <c r="AH252" s="17"/>
       <c r="AI252" s="17"/>
       <c r="AJ252" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK252" s="7"/>
@@ -18142,7 +18142,7 @@
         <v>0</v>
       </c>
       <c r="AP252" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS252" s="14" t="str">
@@ -18154,7 +18154,7 @@
       <c r="A253" s="6"/>
       <c r="B253" s="7"/>
       <c r="C253" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D253" s="17"/>
@@ -18173,11 +18173,11 @@
       <c r="Q253" s="17"/>
       <c r="R253" s="17"/>
       <c r="S253" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T253" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U253" s="17"/>
@@ -18196,7 +18196,7 @@
       <c r="AH253" s="17"/>
       <c r="AI253" s="17"/>
       <c r="AJ253" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK253" s="7"/>
@@ -18211,7 +18211,7 @@
         <v>0</v>
       </c>
       <c r="AP253" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS253" s="14" t="str">
@@ -18223,7 +18223,7 @@
       <c r="A254" s="15"/>
       <c r="B254" s="7"/>
       <c r="C254" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D254" s="17"/>
@@ -18242,11 +18242,11 @@
       <c r="Q254" s="17"/>
       <c r="R254" s="17"/>
       <c r="S254" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T254" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U254" s="17"/>
@@ -18265,7 +18265,7 @@
       <c r="AH254" s="17"/>
       <c r="AI254" s="17"/>
       <c r="AJ254" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK254" s="7"/>
@@ -18280,7 +18280,7 @@
         <v>0</v>
       </c>
       <c r="AP254" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS254" s="14" t="str">
@@ -18292,7 +18292,7 @@
       <c r="A255" s="6"/>
       <c r="B255" s="7"/>
       <c r="C255" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D255" s="17"/>
@@ -18311,11 +18311,11 @@
       <c r="Q255" s="17"/>
       <c r="R255" s="17"/>
       <c r="S255" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T255" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U255" s="17"/>
@@ -18334,7 +18334,7 @@
       <c r="AH255" s="17"/>
       <c r="AI255" s="17"/>
       <c r="AJ255" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK255" s="7"/>
@@ -18349,7 +18349,7 @@
         <v>0</v>
       </c>
       <c r="AP255" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS255" s="14" t="str">
@@ -18361,7 +18361,7 @@
       <c r="A256" s="15"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D256" s="17"/>
@@ -18380,11 +18380,11 @@
       <c r="Q256" s="17"/>
       <c r="R256" s="17"/>
       <c r="S256" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T256" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U256" s="17"/>
@@ -18403,7 +18403,7 @@
       <c r="AH256" s="17"/>
       <c r="AI256" s="17"/>
       <c r="AJ256" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK256" s="7"/>
@@ -18418,7 +18418,7 @@
         <v>0</v>
       </c>
       <c r="AP256" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS256" s="14" t="str">
@@ -18430,7 +18430,7 @@
       <c r="A257" s="6"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D257" s="17"/>
@@ -18449,11 +18449,11 @@
       <c r="Q257" s="17"/>
       <c r="R257" s="17"/>
       <c r="S257" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T257" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U257" s="17"/>
@@ -18472,7 +18472,7 @@
       <c r="AH257" s="17"/>
       <c r="AI257" s="17"/>
       <c r="AJ257" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK257" s="7"/>
@@ -18487,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="AP257" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS257" s="14" t="str">
@@ -18499,7 +18499,7 @@
       <c r="A258" s="15"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D258" s="17"/>
@@ -18518,11 +18518,11 @@
       <c r="Q258" s="17"/>
       <c r="R258" s="17"/>
       <c r="S258" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T258" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U258" s="17"/>
@@ -18541,7 +18541,7 @@
       <c r="AH258" s="17"/>
       <c r="AI258" s="17"/>
       <c r="AJ258" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK258" s="7"/>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="AP258" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS258" s="14" t="str">
@@ -18568,7 +18568,7 @@
       <c r="A259" s="6"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D259" s="17"/>
@@ -18587,11 +18587,11 @@
       <c r="Q259" s="17"/>
       <c r="R259" s="17"/>
       <c r="S259" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T259" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U259" s="17"/>
@@ -18610,7 +18610,7 @@
       <c r="AH259" s="17"/>
       <c r="AI259" s="17"/>
       <c r="AJ259" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK259" s="7"/>
@@ -18625,7 +18625,7 @@
         <v>0</v>
       </c>
       <c r="AP259" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS259" s="14" t="str">
@@ -18637,7 +18637,7 @@
       <c r="A260" s="15"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D260" s="17"/>
@@ -18656,11 +18656,11 @@
       <c r="Q260" s="17"/>
       <c r="R260" s="17"/>
       <c r="S260" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T260" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U260" s="17"/>
@@ -18679,26 +18679,26 @@
       <c r="AH260" s="17"/>
       <c r="AI260" s="17"/>
       <c r="AJ260" s="9">
-        <f t="shared" ref="AJ260:AJ304" si="20">IFERROR(SUM(U260,V260,W260,X260,Y260,Z260,AA260,AB260,AC260,AD260,AE260,AF260,AG260,AH260,AI260)/T260*10,0)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK260" s="7"/>
       <c r="AL260" s="7"/>
       <c r="AM260" s="10"/>
       <c r="AN260" s="11">
-        <f t="shared" ref="AN260:AN304" si="21">ROUND(SUM(B260,S260,AJ260,AK260,AL260,AM260),2)</f>
+        <f t="shared" ref="AN260:AN304" si="23">ROUND(SUM(B260,S260,AJ260,AK260,AL260,AM260),2)</f>
         <v>0</v>
       </c>
       <c r="AO260" s="12">
-        <f t="shared" ref="AO260:AO304" si="22">ROUND(AN260/110*100,1)</f>
+        <f t="shared" ref="AO260:AO304" si="24">ROUND(AN260/110*100,1)</f>
         <v>0</v>
       </c>
       <c r="AP260" s="13" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS260" s="14" t="str">
-        <f t="shared" ref="AS260:AS304" si="23">IF(A260="","",AO260-ROW()/100000000)</f>
+        <f t="shared" ref="AS260:AS304" si="25">IF(A260="","",AO260-ROW()/100000000)</f>
         <v/>
       </c>
     </row>
@@ -18706,7 +18706,7 @@
       <c r="A261" s="6"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="D261" s="17"/>
@@ -18725,11 +18725,11 @@
       <c r="Q261" s="17"/>
       <c r="R261" s="17"/>
       <c r="S261" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T261" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U261" s="17"/>
@@ -18748,26 +18748,26 @@
       <c r="AH261" s="17"/>
       <c r="AI261" s="17"/>
       <c r="AJ261" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK261" s="7"/>
       <c r="AL261" s="7"/>
       <c r="AM261" s="10"/>
       <c r="AN261" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO261" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AP261" s="13" t="str">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP261" s="13" t="str">
-        <f t="shared" si="19"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS261" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -18775,7 +18775,7 @@
       <c r="A262" s="15"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8" t="str">
-        <f t="shared" ref="C262:C304" si="24">IF(COUNTA($D$3:$R$3)=0, "", COUNTA($D$3:$R$3))</f>
+        <f t="shared" ref="C262:C304" si="26">IF(COUNTA($D$3:$R$3)=0, "", COUNTA($D$3:$R$3))</f>
         <v/>
       </c>
       <c r="D262" s="17"/>
@@ -18794,11 +18794,11 @@
       <c r="Q262" s="17"/>
       <c r="R262" s="17"/>
       <c r="S262" s="9">
-        <f t="shared" ref="S262:S304" si="25">IFERROR(ROUND(SUM(D262,E262,F262,G262,H262,I262,J262,K262,L262,M262,N262,O262,P262,Q262,R262)/C262*20,0),0)</f>
+        <f t="shared" ref="S262:S304" si="27">IFERROR(ROUND(SUM(D262,E262,F262,G262,H262,I262,J262,K262,L262,M262,N262,O262,P262,Q262,R262)/C262*20,0),0)</f>
         <v>0</v>
       </c>
       <c r="T262" s="8" t="str">
-        <f t="shared" ref="T262:T304" si="26">IF(COUNTA($U$3:$AI$3 )=0, "", COUNTA($U$3:$AI$3))</f>
+        <f t="shared" ref="T262:T304" si="28">IF(COUNTA($U$3:$AI$3 )=0, "", COUNTA($U$3:$AI$3))</f>
         <v/>
       </c>
       <c r="U262" s="17"/>
@@ -18817,26 +18817,26 @@
       <c r="AH262" s="17"/>
       <c r="AI262" s="17"/>
       <c r="AJ262" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="AJ262:AJ304" si="29">IFERROR(ROUND(SUM(AI262,AH262,AG262,AF262,AE262,AD262,AC262,AB262,AA262,Z262,Y262,X262,W262,V262,U262,)/T262*10,0),0)</f>
         <v>0</v>
       </c>
       <c r="AK262" s="7"/>
       <c r="AL262" s="7"/>
       <c r="AM262" s="10"/>
       <c r="AN262" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO262" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP262" s="13" t="str">
-        <f t="shared" ref="AP262:AP304" si="27">IF(AN262&gt;=90,"A",IF(AN262&gt;=80,"B",IF(AN262&gt;=70,"C",IF(AN262&gt;=60,"D",IF(AN262&gt;0,"F"," ")))))</f>
+        <f t="shared" ref="AP262:AP304" si="30">IF(AN262&gt;=90,"A",IF(AN262&gt;=80,"B",IF(AN262&gt;=70,"C",IF(AN262&gt;=60,"D",IF(AN262&gt;0,"F"," ")))))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS262" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -18844,7 +18844,7 @@
       <c r="A263" s="6"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D263" s="17"/>
@@ -18863,11 +18863,11 @@
       <c r="Q263" s="17"/>
       <c r="R263" s="17"/>
       <c r="S263" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T263" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U263" s="17"/>
@@ -18886,26 +18886,26 @@
       <c r="AH263" s="17"/>
       <c r="AI263" s="17"/>
       <c r="AJ263" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK263" s="7"/>
       <c r="AL263" s="7"/>
       <c r="AM263" s="10"/>
       <c r="AN263" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO263" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP263" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS263" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       <c r="A264" s="15"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D264" s="17"/>
@@ -18932,11 +18932,11 @@
       <c r="Q264" s="17"/>
       <c r="R264" s="17"/>
       <c r="S264" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T264" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U264" s="17"/>
@@ -18955,26 +18955,26 @@
       <c r="AH264" s="17"/>
       <c r="AI264" s="17"/>
       <c r="AJ264" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK264" s="7"/>
       <c r="AL264" s="7"/>
       <c r="AM264" s="10"/>
       <c r="AN264" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO264" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP264" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS264" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -18982,7 +18982,7 @@
       <c r="A265" s="6"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D265" s="17"/>
@@ -19001,11 +19001,11 @@
       <c r="Q265" s="17"/>
       <c r="R265" s="17"/>
       <c r="S265" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T265" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U265" s="17"/>
@@ -19024,26 +19024,26 @@
       <c r="AH265" s="17"/>
       <c r="AI265" s="17"/>
       <c r="AJ265" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK265" s="7"/>
       <c r="AL265" s="7"/>
       <c r="AM265" s="10"/>
       <c r="AN265" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO265" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP265" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS265" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19051,7 +19051,7 @@
       <c r="A266" s="15"/>
       <c r="B266" s="7"/>
       <c r="C266" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D266" s="17"/>
@@ -19070,11 +19070,11 @@
       <c r="Q266" s="17"/>
       <c r="R266" s="17"/>
       <c r="S266" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T266" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U266" s="17"/>
@@ -19093,26 +19093,26 @@
       <c r="AH266" s="17"/>
       <c r="AI266" s="17"/>
       <c r="AJ266" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK266" s="7"/>
       <c r="AL266" s="7"/>
       <c r="AM266" s="10"/>
       <c r="AN266" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO266" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP266" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS266" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19120,7 +19120,7 @@
       <c r="A267" s="6"/>
       <c r="B267" s="7"/>
       <c r="C267" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D267" s="17"/>
@@ -19139,11 +19139,11 @@
       <c r="Q267" s="17"/>
       <c r="R267" s="17"/>
       <c r="S267" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T267" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U267" s="17"/>
@@ -19162,26 +19162,26 @@
       <c r="AH267" s="17"/>
       <c r="AI267" s="17"/>
       <c r="AJ267" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK267" s="7"/>
       <c r="AL267" s="7"/>
       <c r="AM267" s="10"/>
       <c r="AN267" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO267" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP267" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS267" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       <c r="A268" s="15"/>
       <c r="B268" s="7"/>
       <c r="C268" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D268" s="17"/>
@@ -19208,11 +19208,11 @@
       <c r="Q268" s="17"/>
       <c r="R268" s="17"/>
       <c r="S268" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T268" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U268" s="17"/>
@@ -19231,26 +19231,26 @@
       <c r="AH268" s="17"/>
       <c r="AI268" s="17"/>
       <c r="AJ268" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK268" s="7"/>
       <c r="AL268" s="7"/>
       <c r="AM268" s="10"/>
       <c r="AN268" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO268" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP268" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS268" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19258,7 +19258,7 @@
       <c r="A269" s="6"/>
       <c r="B269" s="7"/>
       <c r="C269" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D269" s="17"/>
@@ -19277,11 +19277,11 @@
       <c r="Q269" s="17"/>
       <c r="R269" s="17"/>
       <c r="S269" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T269" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U269" s="17"/>
@@ -19300,26 +19300,26 @@
       <c r="AH269" s="17"/>
       <c r="AI269" s="17"/>
       <c r="AJ269" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK269" s="7"/>
       <c r="AL269" s="7"/>
       <c r="AM269" s="10"/>
       <c r="AN269" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO269" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP269" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS269" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       <c r="A270" s="15"/>
       <c r="B270" s="7"/>
       <c r="C270" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D270" s="17"/>
@@ -19346,11 +19346,11 @@
       <c r="Q270" s="17"/>
       <c r="R270" s="17"/>
       <c r="S270" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T270" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U270" s="17"/>
@@ -19369,26 +19369,26 @@
       <c r="AH270" s="17"/>
       <c r="AI270" s="17"/>
       <c r="AJ270" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK270" s="7"/>
       <c r="AL270" s="7"/>
       <c r="AM270" s="10"/>
       <c r="AN270" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO270" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP270" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS270" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19396,7 +19396,7 @@
       <c r="A271" s="6"/>
       <c r="B271" s="7"/>
       <c r="C271" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D271" s="17"/>
@@ -19415,11 +19415,11 @@
       <c r="Q271" s="17"/>
       <c r="R271" s="17"/>
       <c r="S271" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T271" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U271" s="17"/>
@@ -19438,26 +19438,26 @@
       <c r="AH271" s="17"/>
       <c r="AI271" s="17"/>
       <c r="AJ271" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK271" s="7"/>
       <c r="AL271" s="7"/>
       <c r="AM271" s="10"/>
       <c r="AN271" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO271" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP271" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS271" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       <c r="A272" s="15"/>
       <c r="B272" s="7"/>
       <c r="C272" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D272" s="17"/>
@@ -19484,11 +19484,11 @@
       <c r="Q272" s="17"/>
       <c r="R272" s="17"/>
       <c r="S272" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T272" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U272" s="17"/>
@@ -19507,26 +19507,26 @@
       <c r="AH272" s="17"/>
       <c r="AI272" s="17"/>
       <c r="AJ272" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK272" s="7"/>
       <c r="AL272" s="7"/>
       <c r="AM272" s="10"/>
       <c r="AN272" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO272" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP272" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS272" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
       <c r="A273" s="6"/>
       <c r="B273" s="7"/>
       <c r="C273" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D273" s="17"/>
@@ -19553,11 +19553,11 @@
       <c r="Q273" s="17"/>
       <c r="R273" s="17"/>
       <c r="S273" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T273" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U273" s="17"/>
@@ -19576,26 +19576,26 @@
       <c r="AH273" s="17"/>
       <c r="AI273" s="17"/>
       <c r="AJ273" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK273" s="7"/>
       <c r="AL273" s="7"/>
       <c r="AM273" s="10"/>
       <c r="AN273" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO273" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP273" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS273" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19603,7 +19603,7 @@
       <c r="A274" s="15"/>
       <c r="B274" s="7"/>
       <c r="C274" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D274" s="17"/>
@@ -19622,11 +19622,11 @@
       <c r="Q274" s="17"/>
       <c r="R274" s="17"/>
       <c r="S274" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T274" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U274" s="17"/>
@@ -19645,26 +19645,26 @@
       <c r="AH274" s="17"/>
       <c r="AI274" s="17"/>
       <c r="AJ274" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK274" s="7"/>
       <c r="AL274" s="7"/>
       <c r="AM274" s="10"/>
       <c r="AN274" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO274" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP274" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS274" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19672,7 +19672,7 @@
       <c r="A275" s="6"/>
       <c r="B275" s="7"/>
       <c r="C275" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D275" s="17"/>
@@ -19691,11 +19691,11 @@
       <c r="Q275" s="17"/>
       <c r="R275" s="17"/>
       <c r="S275" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T275" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U275" s="17"/>
@@ -19714,26 +19714,26 @@
       <c r="AH275" s="17"/>
       <c r="AI275" s="17"/>
       <c r="AJ275" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK275" s="7"/>
       <c r="AL275" s="7"/>
       <c r="AM275" s="10"/>
       <c r="AN275" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO275" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP275" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS275" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       <c r="A276" s="15"/>
       <c r="B276" s="7"/>
       <c r="C276" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D276" s="17"/>
@@ -19760,11 +19760,11 @@
       <c r="Q276" s="17"/>
       <c r="R276" s="17"/>
       <c r="S276" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T276" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U276" s="17"/>
@@ -19783,26 +19783,26 @@
       <c r="AH276" s="17"/>
       <c r="AI276" s="17"/>
       <c r="AJ276" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK276" s="7"/>
       <c r="AL276" s="7"/>
       <c r="AM276" s="10"/>
       <c r="AN276" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO276" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP276" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS276" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19810,7 +19810,7 @@
       <c r="A277" s="6"/>
       <c r="B277" s="7"/>
       <c r="C277" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D277" s="17"/>
@@ -19829,11 +19829,11 @@
       <c r="Q277" s="17"/>
       <c r="R277" s="17"/>
       <c r="S277" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T277" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U277" s="17"/>
@@ -19852,26 +19852,26 @@
       <c r="AH277" s="17"/>
       <c r="AI277" s="17"/>
       <c r="AJ277" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK277" s="7"/>
       <c r="AL277" s="7"/>
       <c r="AM277" s="10"/>
       <c r="AN277" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO277" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP277" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS277" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       <c r="A278" s="15"/>
       <c r="B278" s="7"/>
       <c r="C278" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D278" s="17"/>
@@ -19898,11 +19898,11 @@
       <c r="Q278" s="17"/>
       <c r="R278" s="17"/>
       <c r="S278" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T278" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U278" s="17"/>
@@ -19921,26 +19921,26 @@
       <c r="AH278" s="17"/>
       <c r="AI278" s="17"/>
       <c r="AJ278" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK278" s="7"/>
       <c r="AL278" s="7"/>
       <c r="AM278" s="10"/>
       <c r="AN278" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO278" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP278" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS278" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -19948,7 +19948,7 @@
       <c r="A279" s="6"/>
       <c r="B279" s="7"/>
       <c r="C279" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D279" s="17"/>
@@ -19967,11 +19967,11 @@
       <c r="Q279" s="17"/>
       <c r="R279" s="17"/>
       <c r="S279" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T279" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U279" s="17"/>
@@ -19990,26 +19990,26 @@
       <c r="AH279" s="17"/>
       <c r="AI279" s="17"/>
       <c r="AJ279" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK279" s="7"/>
       <c r="AL279" s="7"/>
       <c r="AM279" s="10"/>
       <c r="AN279" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO279" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP279" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS279" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
       <c r="A280" s="15"/>
       <c r="B280" s="7"/>
       <c r="C280" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D280" s="17"/>
@@ -20036,11 +20036,11 @@
       <c r="Q280" s="17"/>
       <c r="R280" s="17"/>
       <c r="S280" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T280" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U280" s="17"/>
@@ -20059,26 +20059,26 @@
       <c r="AH280" s="17"/>
       <c r="AI280" s="17"/>
       <c r="AJ280" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK280" s="7"/>
       <c r="AL280" s="7"/>
       <c r="AM280" s="10"/>
       <c r="AN280" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO280" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP280" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS280" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       <c r="A281" s="6"/>
       <c r="B281" s="7"/>
       <c r="C281" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D281" s="17"/>
@@ -20105,11 +20105,11 @@
       <c r="Q281" s="17"/>
       <c r="R281" s="17"/>
       <c r="S281" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T281" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U281" s="17"/>
@@ -20128,26 +20128,26 @@
       <c r="AH281" s="17"/>
       <c r="AI281" s="17"/>
       <c r="AJ281" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK281" s="7"/>
       <c r="AL281" s="7"/>
       <c r="AM281" s="10"/>
       <c r="AN281" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO281" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP281" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS281" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       <c r="A282" s="15"/>
       <c r="B282" s="7"/>
       <c r="C282" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D282" s="17"/>
@@ -20174,11 +20174,11 @@
       <c r="Q282" s="17"/>
       <c r="R282" s="17"/>
       <c r="S282" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T282" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U282" s="17"/>
@@ -20197,26 +20197,26 @@
       <c r="AH282" s="17"/>
       <c r="AI282" s="17"/>
       <c r="AJ282" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK282" s="7"/>
       <c r="AL282" s="7"/>
       <c r="AM282" s="10"/>
       <c r="AN282" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO282" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP282" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS282" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20224,7 +20224,7 @@
       <c r="A283" s="6"/>
       <c r="B283" s="7"/>
       <c r="C283" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D283" s="17"/>
@@ -20243,11 +20243,11 @@
       <c r="Q283" s="17"/>
       <c r="R283" s="17"/>
       <c r="S283" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T283" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U283" s="17"/>
@@ -20266,26 +20266,26 @@
       <c r="AH283" s="17"/>
       <c r="AI283" s="17"/>
       <c r="AJ283" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK283" s="7"/>
       <c r="AL283" s="7"/>
       <c r="AM283" s="10"/>
       <c r="AN283" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO283" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP283" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS283" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       <c r="A284" s="15"/>
       <c r="B284" s="7"/>
       <c r="C284" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D284" s="17"/>
@@ -20312,11 +20312,11 @@
       <c r="Q284" s="17"/>
       <c r="R284" s="17"/>
       <c r="S284" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T284" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U284" s="17"/>
@@ -20335,26 +20335,26 @@
       <c r="AH284" s="17"/>
       <c r="AI284" s="17"/>
       <c r="AJ284" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK284" s="7"/>
       <c r="AL284" s="7"/>
       <c r="AM284" s="10"/>
       <c r="AN284" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO284" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP284" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS284" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20362,7 +20362,7 @@
       <c r="A285" s="6"/>
       <c r="B285" s="7"/>
       <c r="C285" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D285" s="17"/>
@@ -20381,11 +20381,11 @@
       <c r="Q285" s="17"/>
       <c r="R285" s="17"/>
       <c r="S285" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T285" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U285" s="17"/>
@@ -20404,26 +20404,26 @@
       <c r="AH285" s="17"/>
       <c r="AI285" s="17"/>
       <c r="AJ285" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK285" s="7"/>
       <c r="AL285" s="7"/>
       <c r="AM285" s="10"/>
       <c r="AN285" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO285" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP285" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS285" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       <c r="A286" s="15"/>
       <c r="B286" s="7"/>
       <c r="C286" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D286" s="17"/>
@@ -20450,11 +20450,11 @@
       <c r="Q286" s="17"/>
       <c r="R286" s="17"/>
       <c r="S286" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T286" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U286" s="17"/>
@@ -20473,26 +20473,26 @@
       <c r="AH286" s="17"/>
       <c r="AI286" s="17"/>
       <c r="AJ286" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK286" s="7"/>
       <c r="AL286" s="7"/>
       <c r="AM286" s="10"/>
       <c r="AN286" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO286" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP286" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS286" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20500,7 +20500,7 @@
       <c r="A287" s="6"/>
       <c r="B287" s="7"/>
       <c r="C287" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D287" s="17"/>
@@ -20519,11 +20519,11 @@
       <c r="Q287" s="17"/>
       <c r="R287" s="17"/>
       <c r="S287" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T287" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U287" s="17"/>
@@ -20542,26 +20542,26 @@
       <c r="AH287" s="17"/>
       <c r="AI287" s="17"/>
       <c r="AJ287" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK287" s="7"/>
       <c r="AL287" s="7"/>
       <c r="AM287" s="10"/>
       <c r="AN287" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO287" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP287" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS287" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       <c r="A288" s="15"/>
       <c r="B288" s="7"/>
       <c r="C288" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D288" s="17"/>
@@ -20588,11 +20588,11 @@
       <c r="Q288" s="17"/>
       <c r="R288" s="17"/>
       <c r="S288" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T288" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U288" s="17"/>
@@ -20611,26 +20611,26 @@
       <c r="AH288" s="17"/>
       <c r="AI288" s="17"/>
       <c r="AJ288" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK288" s="7"/>
       <c r="AL288" s="7"/>
       <c r="AM288" s="10"/>
       <c r="AN288" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO288" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP288" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS288" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       <c r="A289" s="6"/>
       <c r="B289" s="7"/>
       <c r="C289" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D289" s="17"/>
@@ -20657,11 +20657,11 @@
       <c r="Q289" s="17"/>
       <c r="R289" s="17"/>
       <c r="S289" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T289" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U289" s="17"/>
@@ -20680,26 +20680,26 @@
       <c r="AH289" s="17"/>
       <c r="AI289" s="17"/>
       <c r="AJ289" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK289" s="7"/>
       <c r="AL289" s="7"/>
       <c r="AM289" s="10"/>
       <c r="AN289" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO289" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP289" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS289" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20707,7 +20707,7 @@
       <c r="A290" s="15"/>
       <c r="B290" s="7"/>
       <c r="C290" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D290" s="17"/>
@@ -20726,11 +20726,11 @@
       <c r="Q290" s="17"/>
       <c r="R290" s="17"/>
       <c r="S290" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T290" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U290" s="17"/>
@@ -20749,26 +20749,26 @@
       <c r="AH290" s="17"/>
       <c r="AI290" s="17"/>
       <c r="AJ290" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK290" s="7"/>
       <c r="AL290" s="7"/>
       <c r="AM290" s="10"/>
       <c r="AN290" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO290" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP290" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS290" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20776,7 +20776,7 @@
       <c r="A291" s="6"/>
       <c r="B291" s="7"/>
       <c r="C291" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D291" s="17"/>
@@ -20795,11 +20795,11 @@
       <c r="Q291" s="17"/>
       <c r="R291" s="17"/>
       <c r="S291" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T291" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U291" s="17"/>
@@ -20818,26 +20818,26 @@
       <c r="AH291" s="17"/>
       <c r="AI291" s="17"/>
       <c r="AJ291" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK291" s="7"/>
       <c r="AL291" s="7"/>
       <c r="AM291" s="10"/>
       <c r="AN291" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO291" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP291" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS291" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       <c r="A292" s="15"/>
       <c r="B292" s="7"/>
       <c r="C292" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D292" s="17"/>
@@ -20864,11 +20864,11 @@
       <c r="Q292" s="17"/>
       <c r="R292" s="17"/>
       <c r="S292" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T292" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U292" s="17"/>
@@ -20887,26 +20887,26 @@
       <c r="AH292" s="17"/>
       <c r="AI292" s="17"/>
       <c r="AJ292" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK292" s="7"/>
       <c r="AL292" s="7"/>
       <c r="AM292" s="10"/>
       <c r="AN292" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO292" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP292" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS292" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20914,7 +20914,7 @@
       <c r="A293" s="6"/>
       <c r="B293" s="7"/>
       <c r="C293" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D293" s="17"/>
@@ -20933,11 +20933,11 @@
       <c r="Q293" s="17"/>
       <c r="R293" s="17"/>
       <c r="S293" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T293" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U293" s="17"/>
@@ -20956,26 +20956,26 @@
       <c r="AH293" s="17"/>
       <c r="AI293" s="17"/>
       <c r="AJ293" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK293" s="7"/>
       <c r="AL293" s="7"/>
       <c r="AM293" s="10"/>
       <c r="AN293" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO293" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP293" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS293" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -20983,7 +20983,7 @@
       <c r="A294" s="15"/>
       <c r="B294" s="7"/>
       <c r="C294" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D294" s="17"/>
@@ -21002,11 +21002,11 @@
       <c r="Q294" s="17"/>
       <c r="R294" s="17"/>
       <c r="S294" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T294" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U294" s="17"/>
@@ -21025,26 +21025,26 @@
       <c r="AH294" s="17"/>
       <c r="AI294" s="17"/>
       <c r="AJ294" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK294" s="7"/>
       <c r="AL294" s="7"/>
       <c r="AM294" s="10"/>
       <c r="AN294" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO294" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP294" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS294" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21052,7 +21052,7 @@
       <c r="A295" s="6"/>
       <c r="B295" s="7"/>
       <c r="C295" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D295" s="17"/>
@@ -21071,11 +21071,11 @@
       <c r="Q295" s="17"/>
       <c r="R295" s="17"/>
       <c r="S295" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T295" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U295" s="17"/>
@@ -21094,26 +21094,26 @@
       <c r="AH295" s="17"/>
       <c r="AI295" s="17"/>
       <c r="AJ295" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK295" s="7"/>
       <c r="AL295" s="7"/>
       <c r="AM295" s="10"/>
       <c r="AN295" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO295" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP295" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS295" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21121,7 +21121,7 @@
       <c r="A296" s="15"/>
       <c r="B296" s="7"/>
       <c r="C296" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D296" s="17"/>
@@ -21140,11 +21140,11 @@
       <c r="Q296" s="17"/>
       <c r="R296" s="17"/>
       <c r="S296" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T296" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U296" s="17"/>
@@ -21163,26 +21163,26 @@
       <c r="AH296" s="17"/>
       <c r="AI296" s="17"/>
       <c r="AJ296" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK296" s="7"/>
       <c r="AL296" s="7"/>
       <c r="AM296" s="10"/>
       <c r="AN296" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO296" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP296" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS296" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21190,7 +21190,7 @@
       <c r="A297" s="6"/>
       <c r="B297" s="7"/>
       <c r="C297" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D297" s="17"/>
@@ -21209,11 +21209,11 @@
       <c r="Q297" s="17"/>
       <c r="R297" s="17"/>
       <c r="S297" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T297" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U297" s="17"/>
@@ -21232,26 +21232,26 @@
       <c r="AH297" s="17"/>
       <c r="AI297" s="17"/>
       <c r="AJ297" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK297" s="7"/>
       <c r="AL297" s="7"/>
       <c r="AM297" s="10"/>
       <c r="AN297" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO297" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP297" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS297" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       <c r="A298" s="15"/>
       <c r="B298" s="7"/>
       <c r="C298" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D298" s="17"/>
@@ -21278,11 +21278,11 @@
       <c r="Q298" s="17"/>
       <c r="R298" s="17"/>
       <c r="S298" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T298" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U298" s="17"/>
@@ -21301,26 +21301,26 @@
       <c r="AH298" s="17"/>
       <c r="AI298" s="17"/>
       <c r="AJ298" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK298" s="7"/>
       <c r="AL298" s="7"/>
       <c r="AM298" s="10"/>
       <c r="AN298" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO298" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP298" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS298" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21328,7 +21328,7 @@
       <c r="A299" s="6"/>
       <c r="B299" s="7"/>
       <c r="C299" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D299" s="17"/>
@@ -21347,11 +21347,11 @@
       <c r="Q299" s="17"/>
       <c r="R299" s="17"/>
       <c r="S299" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T299" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U299" s="17"/>
@@ -21370,26 +21370,26 @@
       <c r="AH299" s="17"/>
       <c r="AI299" s="17"/>
       <c r="AJ299" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK299" s="7"/>
       <c r="AL299" s="7"/>
       <c r="AM299" s="10"/>
       <c r="AN299" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO299" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP299" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS299" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21397,7 +21397,7 @@
       <c r="A300" s="15"/>
       <c r="B300" s="7"/>
       <c r="C300" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D300" s="17"/>
@@ -21416,11 +21416,11 @@
       <c r="Q300" s="17"/>
       <c r="R300" s="17"/>
       <c r="S300" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T300" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U300" s="17"/>
@@ -21439,26 +21439,26 @@
       <c r="AH300" s="17"/>
       <c r="AI300" s="17"/>
       <c r="AJ300" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK300" s="7"/>
       <c r="AL300" s="7"/>
       <c r="AM300" s="10"/>
       <c r="AN300" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO300" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP300" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS300" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21466,7 +21466,7 @@
       <c r="A301" s="6"/>
       <c r="B301" s="7"/>
       <c r="C301" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D301" s="17"/>
@@ -21485,11 +21485,11 @@
       <c r="Q301" s="17"/>
       <c r="R301" s="17"/>
       <c r="S301" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T301" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U301" s="17"/>
@@ -21508,26 +21508,26 @@
       <c r="AH301" s="17"/>
       <c r="AI301" s="17"/>
       <c r="AJ301" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK301" s="7"/>
       <c r="AL301" s="7"/>
       <c r="AM301" s="10"/>
       <c r="AN301" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO301" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP301" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS301" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21535,7 +21535,7 @@
       <c r="A302" s="15"/>
       <c r="B302" s="7"/>
       <c r="C302" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D302" s="17"/>
@@ -21554,11 +21554,11 @@
       <c r="Q302" s="17"/>
       <c r="R302" s="17"/>
       <c r="S302" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T302" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U302" s="17"/>
@@ -21577,26 +21577,26 @@
       <c r="AH302" s="17"/>
       <c r="AI302" s="17"/>
       <c r="AJ302" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK302" s="7"/>
       <c r="AL302" s="7"/>
       <c r="AM302" s="10"/>
       <c r="AN302" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO302" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP302" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS302" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21604,7 +21604,7 @@
       <c r="A303" s="6"/>
       <c r="B303" s="7"/>
       <c r="C303" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D303" s="17"/>
@@ -21623,11 +21623,11 @@
       <c r="Q303" s="17"/>
       <c r="R303" s="17"/>
       <c r="S303" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T303" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U303" s="17"/>
@@ -21646,26 +21646,26 @@
       <c r="AH303" s="17"/>
       <c r="AI303" s="17"/>
       <c r="AJ303" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK303" s="7"/>
       <c r="AL303" s="7"/>
       <c r="AM303" s="10"/>
       <c r="AN303" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO303" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP303" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS303" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -21673,7 +21673,7 @@
       <c r="A304" s="15"/>
       <c r="B304" s="7"/>
       <c r="C304" s="8" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="D304" s="17"/>
@@ -21692,11 +21692,11 @@
       <c r="Q304" s="17"/>
       <c r="R304" s="17"/>
       <c r="S304" s="9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="T304" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="U304" s="17"/>
@@ -21715,26 +21715,26 @@
       <c r="AH304" s="17"/>
       <c r="AI304" s="17"/>
       <c r="AJ304" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AK304" s="7"/>
       <c r="AL304" s="7"/>
       <c r="AM304" s="10"/>
       <c r="AN304" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AO304" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AP304" s="13" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AS304" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -53106,7 +53106,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="decimal" allowBlank="1" sqref="B5:B304" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>50</formula2>
